--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -598,7 +598,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>verified.json zuletzt geschrieben: 2026-07-31 18:21</t>
+          <t>verified.json zuletzt geschrieben: 2026-07-31 18:38</t>
         </is>
       </c>
     </row>
@@ -1396,13 +1396,13 @@
         <v>98</v>
       </c>
       <c r="D25" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G25" t="n">
         <v>367</v>
@@ -17429,9 +17429,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -17449,7 +17449,11 @@
           <t>EAN / GTIN barcode of the product.</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>filter: no sample value on the test instance — filter not probed | search: probed with a fixture value — no sampled record carries this field</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -17694,9 +17698,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -17714,7 +17718,11 @@
           <t>Manufacturer's own article number (MPN).</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>filter: no sample value on the test instance — filter not probed</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -18906,7 +18914,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>create: created prd_61991 (labelled 'VT Verify') — no delete endpoint, left in place</t>
+          <t>create: created prd_61992 (labelled 'VT Verify') — no delete endpoint, left in place</t>
         </is>
       </c>
     </row>
@@ -21499,9 +21507,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -21519,11 +21527,7 @@
           <t>Whether this is the matrix (parent) product of a variant set. Filterable — the upstream key is isMatrixProduct.</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>filter: filter[variant.isMatrix] 400: Invalid value: False. Valid values are: true, false. {"matrixprodukt": ["Invalid value: False. Valid values are: true, false."]}</t>
-        </is>
-      </c>
+      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -598,7 +598,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>verified.json zuletzt geschrieben: 2026-07-31 18:38</t>
+          <t>verified.json zuletzt geschrieben: 2026-08-01 07:25</t>
         </is>
       </c>
     </row>
@@ -836,10 +836,10 @@
         <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>All postal addresses of the partner: one default 'both' row (the main address) plus an optional deviating billing address and any number of shipping addresses. Writing this collection carries the FULL desired set: an entry without an `id` is created, an entry with an `id` is updated, and any entry you omit is DELETED upstream. It is not an append — to change one row, read them all, edit the one, and send the whole list back.</t>
+          <t>All postal addresses of the partner: one default 'both' row (the main address) plus an optional deviating billing address and any number of shipping addresses. Writing this collection carries the FULL desired set: an entry without an `id` is created, an entry with an `id` is updated, and any entry you omit is DELETED upstream. It is not an append — to change one row, read them all, edit the one, and send the whole list back. `null` means NOT LOADED, not empty: bigger list pages skip the sub-resource read, and a write that carries `null` leaves the collection untouched. Only a list you read from a record (`get`) or a small page is the complete set — never send a `null`-sourced one back as if it were.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Contact persons at the partner (each an individual, differentiated by role/department). Writing this collection carries the FULL desired set: an entry without an `id` is created, an entry with an `id` is updated, and any entry you omit is DELETED upstream. It is not an append — to change one row, read them all, edit the one, and send the whole list back.</t>
+          <t>Contact persons at the partner (each an individual, differentiated by role/department). Writing this collection carries the FULL desired set: an entry without an `id` is created, an entry with an `id` is updated, and any entry you omit is DELETED upstream. It is not an append — to change one row, read them all, edit the one, and send the whole list back. `null` means NOT LOADED, not empty: bigger list pages skip the sub-resource read, and a write that carries `null` leaves the collection untouched. Only a list you read from a record (`get`) or a small page is the complete set — never send a `null`-sourced one back as if it were.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>All postal addresses of the partner: one default 'both' row (the main address) plus an optional deviating billing address and any number of shipping addresses. Writing this collection carries the FULL desired set: an entry without an `id` is created, an entry with an `id` is updated, and any entry you omit is DELETED upstream. It is not an append — to change one row, read them all, edit the one, and send the whole list back.</t>
+          <t>All postal addresses of the partner: one default 'both' row (the main address) plus an optional deviating billing address and any number of shipping addresses. Writing this collection carries the FULL desired set: an entry without an `id` is created, an entry with an `id` is updated, and any entry you omit is DELETED upstream. It is not an append — to change one row, read them all, edit the one, and send the whole list back. `null` means NOT LOADED, not empty: bigger list pages skip the sub-resource read, and a write that carries `null` leaves the collection untouched. Only a list you read from a record (`get`) or a small page is the complete set — never send a `null`-sourced one back as if it were.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Contact persons at the partner (each an individual, differentiated by role/department). Writing this collection carries the FULL desired set: an entry without an `id` is created, an entry with an `id` is updated, and any entry you omit is DELETED upstream. It is not an append — to change one row, read them all, edit the one, and send the whole list back.</t>
+          <t>Contact persons at the partner (each an individual, differentiated by role/department). Writing this collection carries the FULL desired set: an entry without an `id` is created, an entry with an `id` is updated, and any entry you omit is DELETED upstream. It is not an append — to change one row, read them all, edit the one, and send the whole list back. `null` means NOT LOADED, not empty: bigger list pages skip the sub-resource read, and a write that carries `null` leaves the collection untouched. Only a list you read from a record (`get`) or a small page is the complete set — never send a `null`-sourced one back as if it were.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -72001,9 +72001,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -72031,11 +72031,7 @@
           <t>Free-text description of the line (extends or overrides the product name).</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>create: sent on create but did not persist on the created record</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -598,7 +598,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>verified.json zuletzt geschrieben: 2026-08-01 07:25</t>
+          <t>verified.json zuletzt geschrieben: 2026-08-01 07:53</t>
         </is>
       </c>
     </row>
@@ -836,10 +836,10 @@
         <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -1316,10 +1316,10 @@
         <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>7</v>
@@ -1396,10 +1396,10 @@
         <v>98</v>
       </c>
       <c r="D25" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
         <v>53</v>
@@ -1716,13 +1716,13 @@
         <v>17</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -8030,7 +8030,11 @@
           <t>Timestamp the record was created.</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>filter: accepts the date part only, not the full timestamp it returns on read</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -10222,7 +10226,11 @@
           <t>Timestamp the record was last changed.</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>filter: accepts the date part only, not the full timestamp it returns on read</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -12755,7 +12763,11 @@
           <t>Timestamp the record was created.</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>filter: accepts the date part only, not the full timestamp it returns on read</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -13853,7 +13865,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>create: created sup_20456 but DELETE returned 405 — manual cleanup needed (record is named 'VT Verify GmbH')</t>
+          <t>create: created sup_20460 but DELETE returned 405 — manual cleanup needed (record is named 'VT Verify GmbH')</t>
         </is>
       </c>
     </row>
@@ -14770,7 +14782,11 @@
           <t>Timestamp the record was last changed.</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>filter: accepts the date part only, not the full timestamp it returns on read</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -18914,7 +18930,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>create: created prd_61992 (labelled 'VT Verify') — no delete endpoint, left in place</t>
+          <t>create: created prd_61993 (labelled 'VT Verify') — no delete endpoint, left in place</t>
         </is>
       </c>
     </row>
@@ -19151,9 +19167,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -19176,11 +19192,7 @@
           <t>Purchase price amount.</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>update: PATCH 400: Request payload validation failed. {"calculatedPurchasePrice": {"price": {"amount": ["Field `amount` should be a positive int, float or string formatted int or float."]}}}</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -22768,9 +22780,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -22793,11 +22805,7 @@
           <t>Net unit price amount.</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>update: PATCH 400: Request payload validation failed. {"price": {"amount": ["Field `amount` should be a valid string containing floating point number."]}}</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -23414,9 +23422,9 @@
           <t>Created at</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -23467,9 +23475,9 @@
           <t>ID</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -23520,19 +23528,19 @@
           <t>Standard supplier</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -23568,19 +23576,19 @@
           <t>Min quantity</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -23616,9 +23624,9 @@
           <t>Object</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -23669,21 +23677,21 @@
           <t>Package amount</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>–</t>
@@ -23699,7 +23707,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>update: no sample numeric value — not probed (a null number cannot be restored)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23717,14 +23729,14 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -23732,9 +23744,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -23765,19 +23777,19 @@
           <t>Remark</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -23813,24 +23825,24 @@
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -23861,19 +23873,19 @@
           <t>Supplier designation</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -23909,19 +23921,19 @@
           <t>Supplier item number</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -23957,9 +23969,9 @@
           <t>Unit price</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -24005,19 +24017,19 @@
           <t>Amount</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -24053,19 +24065,19 @@
           <t>Currency</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>FEHLER</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -24083,7 +24095,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>update: upstream accepted the write but the value did not persist</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24101,9 +24117,9 @@
           <t>Updated at</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -24154,21 +24170,21 @@
           <t>Valid from</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
           <t>–</t>
@@ -24184,7 +24200,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>update: no sample date value — not probed (a null date cannot be restored)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -24202,21 +24222,21 @@
           <t>Valid until</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
           <t>–</t>
@@ -24232,7 +24252,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>update: no sample date value — not probed (a null date cannot be restored)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -72001,9 +72025,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>FEHLER</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -72031,7 +72055,11 @@
           <t>Free-text description of the line (extends or overrides the product name).</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>create: sent on create but did not persist on the created record</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -598,7 +598,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>verified.json zuletzt geschrieben: 2026-08-01 07:53</t>
+          <t>verified.json zuletzt geschrieben: 2026-08-01 08:11</t>
         </is>
       </c>
     </row>
@@ -836,10 +836,10 @@
         <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -8030,11 +8030,7 @@
           <t>Timestamp the record was created.</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>filter: accepts the date part only, not the full timestamp it returns on read</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -10226,11 +10222,7 @@
           <t>Timestamp the record was last changed.</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>filter: accepts the date part only, not the full timestamp it returns on read</t>
-        </is>
-      </c>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -12763,11 +12755,7 @@
           <t>Timestamp the record was created.</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>filter: accepts the date part only, not the full timestamp it returns on read</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -13865,7 +13853,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>create: created sup_20460 but DELETE returned 405 — manual cleanup needed (record is named 'VT Verify GmbH')</t>
+          <t>create: created sup_20462 but DELETE returned 405 — manual cleanup needed (record is named 'VT Verify GmbH')</t>
         </is>
       </c>
     </row>
@@ -14782,11 +14770,7 @@
           <t>Timestamp the record was last changed.</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>filter: accepts the date part only, not the full timestamp it returns on read</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -72025,9 +72009,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -72055,11 +72039,7 @@
           <t>Free-text description of the line (extends or overrides the product name).</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>create: sent on create but did not persist on the created record</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -598,7 +598,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>verified.json zuletzt geschrieben: 2026-08-01 07:25</t>
+          <t>verified.json zuletzt geschrieben: 2026-08-01 08:11</t>
         </is>
       </c>
     </row>
@@ -1316,10 +1316,10 @@
         <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>7</v>
@@ -1396,10 +1396,10 @@
         <v>98</v>
       </c>
       <c r="D25" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
         <v>53</v>
@@ -1716,13 +1716,13 @@
         <v>17</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>create: created sup_20456 but DELETE returned 405 — manual cleanup needed (record is named 'VT Verify GmbH')</t>
+          <t>create: created sup_20462 but DELETE returned 405 — manual cleanup needed (record is named 'VT Verify GmbH')</t>
         </is>
       </c>
     </row>
@@ -18914,7 +18914,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>create: created prd_61992 (labelled 'VT Verify') — no delete endpoint, left in place</t>
+          <t>create: created prd_61993 (labelled 'VT Verify') — no delete endpoint, left in place</t>
         </is>
       </c>
     </row>
@@ -19151,9 +19151,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -19176,11 +19176,7 @@
           <t>Purchase price amount.</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>update: PATCH 400: Request payload validation failed. {"calculatedPurchasePrice": {"price": {"amount": ["Field `amount` should be a positive int, float or string formatted int or float."]}}}</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -22768,9 +22764,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -22793,11 +22789,7 @@
           <t>Net unit price amount.</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>update: PATCH 400: Request payload validation failed. {"price": {"amount": ["Field `amount` should be a valid string containing floating point number."]}}</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -23414,9 +23406,9 @@
           <t>Created at</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -23467,9 +23459,9 @@
           <t>ID</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -23520,19 +23512,19 @@
           <t>Standard supplier</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -23568,19 +23560,19 @@
           <t>Min quantity</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -23616,9 +23608,9 @@
           <t>Object</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -23669,21 +23661,21 @@
           <t>Package amount</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>–</t>
@@ -23699,7 +23691,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>update: no sample numeric value — not probed (a null number cannot be restored)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23717,14 +23713,14 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -23732,9 +23728,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -23765,19 +23761,19 @@
           <t>Remark</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -23813,24 +23809,24 @@
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -23861,19 +23857,19 @@
           <t>Supplier designation</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -23909,19 +23905,19 @@
           <t>Supplier item number</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -23957,9 +23953,9 @@
           <t>Unit price</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -24005,19 +24001,19 @@
           <t>Amount</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -24053,19 +24049,19 @@
           <t>Currency</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>FEHLER</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -24083,7 +24079,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>update: upstream accepted the write but the value did not persist</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24101,9 +24101,9 @@
           <t>Updated at</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -24154,21 +24154,21 @@
           <t>Valid from</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
           <t>–</t>
@@ -24184,7 +24184,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>update: no sample date value — not probed (a null date cannot be restored)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -24202,21 +24206,21 @@
           <t>Valid until</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
           <t>–</t>
@@ -24232,7 +24236,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>update: no sample date value — not probed (a null date cannot be restored)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -598,7 +598,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>verified.json zuletzt geschrieben: 2026-08-01 08:11</t>
+          <t>verified.json zuletzt geschrieben: 2026-08-01 08:34</t>
         </is>
       </c>
     </row>
@@ -1396,16 +1396,16 @@
         <v>98</v>
       </c>
       <c r="D25" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G25" t="n">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="H25" t="n">
         <v>13</v>
@@ -18014,14 +18014,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -18044,11 +18044,7 @@
           <t>Unit of the dimensions (e.g. cm).</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>update: upstream accepted the write but the value did not persist</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -18283,14 +18279,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -18313,11 +18309,7 @@
           <t>Unit of the net weight (e.g. kg).</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>update: upstream accepted the write but the value did not persist</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -18613,14 +18605,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -18643,11 +18635,7 @@
           <t>Unit of the gross weight (e.g. kg).</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>update: upstream accepted the write but the value did not persist</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -18914,7 +18902,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>create: created prd_61993 (labelled 'VT Verify') — no delete endpoint, left in place</t>
+          <t>create: created prd_61994 (labelled 'VT Verify') — no delete endpoint, left in place</t>
         </is>
       </c>
     </row>
@@ -19591,9 +19579,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -19941,9 +19929,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -21017,9 +21005,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -21211,7 +21199,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>select</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -21229,9 +21217,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -21254,11 +21242,7 @@
           <t>Serial-number tracking mode for the product.</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>update: upstream accepted the write but the value did not persist</t>
-        </is>
-      </c>
+      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -598,7 +598,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>verified.json zuletzt geschrieben: 2026-08-01 08:34</t>
+          <t>verified.json zuletzt geschrieben: 2026-08-01 09:29</t>
         </is>
       </c>
     </row>
@@ -1316,10 +1316,10 @@
         <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>7</v>
@@ -1396,10 +1396,10 @@
         <v>98</v>
       </c>
       <c r="D25" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>47</v>
@@ -1716,10 +1716,10 @@
         <v>17</v>
       </c>
       <c r="D33" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>12</v>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>create: created prd_61994 (labelled 'VT Verify') — no delete endpoint, left in place</t>
+          <t>create: created prd_61995 (labelled 'VT Verify') — no delete endpoint, left in place</t>
         </is>
       </c>
     </row>
@@ -19192,9 +19192,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -19217,11 +19217,7 @@
           <t>Currency of the purchase price.</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>update: upstream accepted the write but the value did not persist</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -22854,9 +22850,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -22879,11 +22875,7 @@
           <t>Currency of the unit price.</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>update: upstream accepted the write but the value did not persist</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -24043,9 +24035,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -24063,11 +24055,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>update: upstream accepted the write but the value did not persist</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -130,7 +130,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -162,11 +162,6 @@
         <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4B183"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -180,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -196,9 +191,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -598,7 +590,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>verified.json zuletzt geschrieben: 2026-08-01 09:29</t>
+          <t>verified.json zuletzt geschrieben: 2026-08-01 10:41</t>
         </is>
       </c>
     </row>
@@ -1396,10 +1388,10 @@
         <v>98</v>
       </c>
       <c r="D25" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>47</v>
@@ -16409,7 +16401,11 @@
           <t>The product's DIRECT components — one level only. Each component is itself a product, so a full explosion means reading each child in turn until its bom.items is empty; there is no roll-up upstream. Filled on a single read only: in a list bom.items is always empty.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16462,7 +16458,11 @@
           <t>REPLACES the whole bill of materials on a create/update — this is not an append. Send every line you want to keep: a line you omit is DELETED, and [] clears the bill entirely. To change one quantity, read the product, edit that number, and send all lines back. If only this composition fails the product is still written and the response carries `_warnings.bom` — a 200/201 does not by itself mean the bill was set.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16515,7 +16515,11 @@
           <t>Component product used in the assembly.</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16568,7 +16572,11 @@
           <t>How much of this component ONE unit of the parent needs — not a stock figure.</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16616,7 +16624,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16669,7 +16681,11 @@
           <t>Omitted on a write, the upstream assigns 'shopping part' (observed on mvp).</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18902,7 +18918,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>create: created prd_61995 (labelled 'VT Verify') — no delete endpoint, left in place</t>
+          <t>create: created prd_61996 (labelled 'VT Verify') — no delete endpoint, left in place</t>
         </is>
       </c>
     </row>
@@ -19355,9 +19371,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -19382,7 +19398,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>update: upstream accepted the write but the value did not persist</t>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
         </is>
       </c>
     </row>
@@ -19412,9 +19428,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -19439,7 +19455,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>update: upstream accepted the write but the value did not persist</t>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
         </is>
       </c>
     </row>
@@ -19705,7 +19721,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -19753,7 +19773,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -19801,7 +19825,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -19849,7 +19877,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -19897,7 +19929,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -20056,7 +20092,11 @@
           <t>Read-only stock figures, all in the product's own unit (see `unit`) — the numbers are bare, they carry no unit of their own. Filled on a single read only; in a list every figure is null. `physical` is what lies on the shelf, `available` what may still be sold; they are NOT the same number.</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -20109,7 +20149,11 @@
           <t>What may still be sold (upstream 'sellable'). NOT what lies on the shelf — see physical — and NOT simply physical minus reserved: demand from open sales orders is deducted too, and the result is floored at 0. Observed on mvp: physical 6, reserved 1, openSalesOrders 3 → available 3.</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -20162,7 +20206,11 @@
           <t>available &lt; logistics.minimumStockQuantity. Null when either side is unknown — never defaulted to false.</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -20215,7 +20263,11 @@
           <t>Xentral's own derived stock figure. The spec's example suggests physical + correction, but every value measured on mvp tracked `available` instead (0/3/17). Undocumented upstream — prefer physical or available, whichever the question actually needs.</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -20268,7 +20320,11 @@
           <t>Manual up/down adjustment applied to the stock figure before it is published (e.g. a safety buffer held back from a shop). A publication mechanic, not a physical fact.</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -20378,7 +20434,11 @@
           <t>Quantity demanded by open sales orders, not yet shipped.</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -20431,7 +20491,11 @@
           <t>What is actually on the shelf, across all warehouses.</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -20484,7 +20548,11 @@
           <t>How many could be built from the components on hand: the minimum over the bill of materials, computed on each component's AVAILABLE quantity — not its physical stock. Null for a product without a bill of materials. Verified on mvp: components at available 17 and 3 → producible 3, while the constrained component's physical stock was 6.</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -20537,7 +20605,11 @@
           <t>A formula-driven stand-in figure reported instead of the real one; null when none is configured.</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -20590,7 +20662,11 @@
           <t>The quantity Xentral reports as committed. Do NOT compute availability from it: available deducts open order demand, not this figure — observed physical 6 / reserved 1 / available 3. What exactly Xentral counts here is not documented upstream.</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>read: populated on a single-record read only; a list leaves it null and names the section in extra.unavailableSections</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -590,7 +590,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>verified.json zuletzt geschrieben: 2026-08-01 10:41</t>
+          <t>verified.json zuletzt geschrieben: 2026-08-01 16:21</t>
         </is>
       </c>
     </row>
@@ -828,28 +828,28 @@
         <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H11" t="n">
         <v>14</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6 (0/0)</t>
+          <t>6 (3/0)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2 (0/0)</t>
+          <t>2 (1/0)</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7 (0/0)</t>
+          <t>7 (2/0)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -908,7 +908,7 @@
         <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -920,16 +920,16 @@
         <v>253</v>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7 (0/0)</t>
+          <t>7 (4/0)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4 (0/0)</t>
+          <t>4 (3/0)</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1 (0/0)</t>
+          <t>1 (1/0)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1 (0/0)</t>
+          <t>1 (1/0)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1668,7 +1668,7 @@
         <v>73</v>
       </c>
       <c r="D32" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1677,19 +1677,19 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H32" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>9 (0/0)</t>
+          <t>9 (3/0)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>3 (0/0)</t>
+          <t>3 (3/0)</t>
         </is>
       </c>
     </row>
@@ -1748,28 +1748,28 @@
         <v>81</v>
       </c>
       <c r="D34" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6 (0/0)</t>
+          <t>6 (3/0)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>4 (0/0)</t>
+          <t>4 (2/0)</t>
         </is>
       </c>
     </row>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8 (0/0)</t>
+          <t>8 (4/0)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>5 (0/0)</t>
+          <t>5 (3/0)</t>
         </is>
       </c>
     </row>
@@ -1868,28 +1868,28 @@
         <v>90</v>
       </c>
       <c r="D37" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G37" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H37" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8 (0/0)</t>
+          <t>8 (3/0)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2 (0/0)</t>
+          <t>2 (2/0)</t>
         </is>
       </c>
     </row>
@@ -1908,28 +1908,28 @@
         <v>121</v>
       </c>
       <c r="D38" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G38" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H38" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>13 (0/0)</t>
+          <t>13 (6/0)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4 (0/0)</t>
+          <t>4 (4/0)</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6 (0/0)</t>
+          <t>6 (5/0)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>7 (0/0)</t>
+          <t>7 (2/0)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5912,7 +5912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -10648,9 +10648,9 @@
           <t>Add a tag to this record (created automatically if new).</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -10672,9 +10672,9 @@
           <t>Remove a tag from this record.</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -10763,6 +10763,79 @@
       <c r="F101" t="inlineStr">
         <is>
           <t>No archive flag is writable via v3 customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>Wünsche ohne Feld (Lücke im Modell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Feld</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Facetten</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Begründung</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>contacts.address</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>create, read, update</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>contacts.isPrimary</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>create, read, update</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Mark the main contact person — v3 contactPersons carry no primary flag.</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15280,9 +15353,9 @@
           <t>Add a tag to this record (created automatically if new).</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -15304,9 +15377,9 @@
           <t>Remove a tag from this record.</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -15395,6 +15468,79 @@
       <c r="F97" t="inlineStr">
         <is>
           <t>No archive flag is writable via v1 suppliers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>Wünsche ohne Feld (Lücke im Modell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Feld</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Facetten</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Begründung</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>contacts.address</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>create, read, update</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>contacts.isPrimary</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>create, read, update</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Mark the main contact person — v3 contactPersons carry no primary flag.</t>
         </is>
       </c>
     </row>
@@ -29547,7 +29693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -31026,9 +31172,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -31052,11 +31198,7 @@
           <t>Quoted line items (products / services).</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>update: Edit quote positions after creation — the v3 update DTO carries no line-item write path.</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -31138,9 +31280,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -31192,9 +31334,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -31563,14 +31705,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -31730,9 +31872,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -31887,14 +32029,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -31918,7 +32060,11 @@
           <t>Tax rate key applied to the line.</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>create: Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream. | update: Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -32098,9 +32244,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -34096,9 +34242,9 @@
           <t>Send the quote to the customer (v3 send — mails the document).</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -34192,9 +34338,9 @@
           <t>Add a tag to this record (created automatically if new).</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -34216,9 +34362,9 @@
           <t>Remove a tag from this record.</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -34275,9 +34421,9 @@
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -34343,12 +34489,63 @@
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>Wünsche ohne Feld (Lücke im Modell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Feld</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Facetten</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Begründung</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>items.totals.tax</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:L85"/>
@@ -35749,9 +35946,9 @@
           <t>Einlagern: book stock ONTO this location. Irreversible — a mistake is corrected by a counter-booking, not by an undo.</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -35777,9 +35974,9 @@
           <t>Auslagern: book stock OFF this location. Reduces stock and cannot be undone — only counter-booked.</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -35801,9 +35998,9 @@
           <t>Umlagern: move stock from THIS location to another one. Not atomic upstream — on a partial failure the removal is compensated and the outcome reported.</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -35825,9 +36022,9 @@
           <t>Inventur: record the COUNTED quantity of a product on this location; the difference to the book quantity is posted. The only repeatable stock write — counting the same result twice posts nothing the second time.</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -35853,9 +36050,9 @@
           <t>Bestandskorrektur: post a known difference against this location. Requires a reason. Use inventoryCount when the counted quantity is known instead of the difference.</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -45140,9 +45337,9 @@
           <t>Create a REAL print job for a base64-encoded PDF on this printer (paper comes out — confirm intent first).</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -45780,9 +45977,9 @@
           <t>Send a REAL email from this account (auditable in Xentral, irreversible — confirm intent first). Xentral appends the sender's configured signature automatically: do NOT write a closing block in `body`, end with the last sentence. Pass `customer` (the Customer record id) whenever the recipient is a known customer so the logged correspondence entry lands on their CRM tab.</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -45845,7 +46042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L148"/>
+  <dimension ref="A1:L152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -47009,9 +47206,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -47042,7 +47239,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>create: Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today. | update: Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today. | filter: no sample value on the test instance — filter not probed</t>
+          <t>update: Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today. | filter: no sample value on the test instance — filter not probed</t>
         </is>
       </c>
     </row>
@@ -47928,9 +48125,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -48198,9 +48395,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -48224,11 +48421,7 @@
           <t>Order line items. On UPDATE this REPLACES the line-item set: an item with an existing items.id is changed, one without an id is added, and any existing item you omit is removed. Send the full desired list (echo back the ids you want to keep).</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>update: Edit order positions (quantities, add/remove articles) after creation — the v3 update DTO carries no line-item write path.</t>
-        </is>
-      </c>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -48532,7 +48725,11 @@
           <t>Free-text description of the line (extends or overrides the product name).</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>update: no sample value for description — not probed (a null line value cannot be restored net-zero)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -48560,9 +48757,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -49089,14 +49286,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -49256,9 +49453,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -49413,14 +49610,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -49444,7 +49641,11 @@
           <t>Tax rate key applied to the line.</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>create: Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream. | update: Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -49634,9 +49835,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -50522,9 +50723,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
@@ -50550,7 +50751,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>create: The customer's own order / PO number (B2B standard field). Read-only upstream today; a clerk must be able to set and correct it. | update: The customer's own order / PO number (B2B standard field). Read-only upstream today; a clerk must be able to set and correct it. | filter: no sample value on the test instance — filter not probed | search: On the phone the customer quotes their PO number, not the ERP number — the full-text search must reach it.</t>
+          <t>create: The customer's own order / PO number (B2B standard field). Read-only upstream today; a clerk must be able to set and correct it. | filter: no sample value on the test instance — filter not probed | search: On the phone the customer quotes their PO number, not the ERP number — the full-text search must reach it.</t>
         </is>
       </c>
     </row>
@@ -52590,9 +52791,9 @@
           <t>Creates the invoice from this order (v3 invoices createFromSalesOrder).</t>
         </is>
       </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -52710,9 +52911,9 @@
           <t>Splits off an EMPTY partial order (raw v1 createPartialSalesOrder); fill it yourself. Prefer splitOrder to move items in one step.</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -52738,9 +52939,9 @@
           <t>Move the given items/quantities into a NEW partial order in one step: creates the partial (v1 createPartialSalesOrder), adds the moved quantities to it, and reduces this order to the remainder (a line fully moved is removed). Together the two orders equal the original demand.</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -52814,9 +53015,9 @@
           <t>Sends the order confirmation to the customer (v3 send — mails the document).</t>
         </is>
       </c>
-      <c r="E139" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -52838,9 +53039,9 @@
           <t>Add a tag to this record (created automatically if new).</t>
         </is>
       </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -52862,9 +53063,9 @@
           <t>Remove a tag from this record.</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -52921,9 +53122,9 @@
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -52941,9 +53142,9 @@
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -52961,9 +53162,9 @@
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
-      <c r="E147" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -52989,12 +53190,63 @@
           <t>Hands the order to logistics (Autoversand): creates a pick run and delivery note and starts shipping. Requires a released/confirmed order with positions. Optional command {printPickList: true} prints the pick list.</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>Wünsche ohne Feld (Lücke im Modell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Feld</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Facetten</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Begründung</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>items.totals.tax</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:L125"/>
@@ -58940,7 +59192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -61169,9 +61421,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -61195,11 +61447,7 @@
           <t>Invoice line items.</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>update: Edit invoice positions after creation — the v3 update DTO carries no line-item write path.</t>
-        </is>
-      </c>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -61307,7 +61555,11 @@
           <t>Free-text description of the line (extends or overrides the product name).</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>update: no sample value for description — not probed (a null line value cannot be restored net-zero)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -61335,9 +61587,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -61648,14 +61900,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -61815,9 +62067,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -61972,14 +62224,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -62003,7 +62255,11 @@
           <t>Tax rate key applied to the line.</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>create: Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream. | update: Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -62193,9 +62449,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -63287,9 +63543,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
@@ -63315,7 +63571,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>create: The customer's PO number on the invoice (B2B) — read-only upstream today; must be settable and correctable. | update: The customer's PO number on the invoice (B2B) — read-only upstream today; must be settable and correctable. | filter: no sample value on the test instance — filter not probed | search: Support and accounting find invoices by the customer's PO number.</t>
+          <t>create: The customer's PO number on the invoice (B2B) — read-only upstream today; must be settable and correctable. | filter: no sample value on the test instance — filter not probed | search: Support and accounting find invoices by the customer's PO number.</t>
         </is>
       </c>
     </row>
@@ -63511,9 +63767,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -63537,11 +63793,7 @@
           <t>Tax scheme applied (domestic / EU B2B / EU OSS / export).</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>update: Correcting the taxation scheme (domestic/euB2B/euOss/export) on an invoice — not updatable upstream today.</t>
-        </is>
-      </c>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -63985,9 +64237,9 @@
           <t>Send the invoice to the customer (v3 send — mails the document).</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -64129,9 +64381,9 @@
           <t>Add a tag to this record (created automatically if new).</t>
         </is>
       </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -64153,9 +64405,9 @@
           <t>Remove a tag from this record.</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -64212,9 +64464,9 @@
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -64240,12 +64492,63 @@
           <t>Cancels a released invoice by creating a cancellation credit note (Storno-Gutschrift) — the GoBD-compliant reversal. A released invoice is write-protected and cannot be status-cancelled; this creates a new counter-document and marks the invoice cancelled. Not reversible; several credit notes may exist per invoice. A DRAFT invoice has no number — discard it with `delete` instead. Optional command {documentNumber} sets the credit note number. The created credit note is returned under `result`.</t>
         </is>
       </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>Wünsche ohne Feld (Lücke im Modell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Feld</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Facetten</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Begründung</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>items.totals.tax</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:L94"/>
@@ -71343,9 +71646,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
@@ -71371,7 +71674,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>create: The customer's PO number on the delivery note (B2B) — read-only upstream today; must be settable. | update: The customer's PO number on the delivery note (B2B) — read-only upstream today; must be settable. | filter: no sample value on the test instance — filter not probed | search: Warehouse/support find a delivery note by the customer's PO number.</t>
+          <t>create: The customer's PO number on the delivery note (B2B) — read-only upstream today; must be settable. | filter: no sample value on the test instance — filter not probed | search: Warehouse/support find a delivery note by the customer's PO number.</t>
         </is>
       </c>
     </row>
@@ -71890,9 +72193,9 @@
           <t>Creates a return for items of this delivery note (v3 returnOrders createFromDeliveryNote). The command must carry lineItems [{id, quantity, returnReason: {id}}].</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -71914,9 +72217,9 @@
           <t>Creates the invoice from this delivery note (v3 invoices createFromDeliveryNote).</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -71986,9 +72289,9 @@
           <t>Add a tag to this record (created automatically if new).</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -72010,9 +72313,9 @@
           <t>Remove a tag from this record.</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -72069,9 +72372,9 @@
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -72113,9 +72416,9 @@
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -72133,9 +72436,9 @@
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -72152,7 +72455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -73417,9 +73720,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -73443,11 +73746,7 @@
           <t>Credit note line items.</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>update: Edit credit-note positions after creation — the v3 update DTO carries no line-item write path.</t>
-        </is>
-      </c>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -73555,7 +73854,11 @@
           <t>Free-text description of the line (extends or overrides the product name).</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>update: no sample value for description — not probed (a null line value cannot be restored net-zero)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -73583,9 +73886,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -73896,14 +74199,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -74063,9 +74366,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -74220,14 +74523,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -74251,7 +74554,11 @@
           <t>Tax rate key applied to the line.</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>create: Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream. | update: Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -74431,9 +74738,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -74925,9 +75232,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -74953,7 +75260,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>create: The customer's PO number on the credit note (B2B) — read-only upstream today. | update: The customer's PO number on the credit note (B2B) — read-only upstream today. | filter: no sample value on the test instance — filter not probed</t>
+          <t>create: The customer's PO number on the credit note (B2B) — read-only upstream today. | filter: no sample value on the test instance — filter not probed</t>
         </is>
       </c>
     </row>
@@ -75937,9 +76244,9 @@
           <t>Send the credit note to the customer (v3 send — mails the document).</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -76033,9 +76340,9 @@
           <t>Add a tag to this record (created automatically if new).</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -76057,9 +76364,9 @@
           <t>Remove a tag from this record.</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -76116,9 +76423,9 @@
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -76144,6 +76451,57 @@
       <c r="F85" t="inlineStr">
         <is>
           <t>A released credit note can only be cancelled in the Xentral UI (legacy); v3 exposes no cancel action. Drafts are removed with `delete`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>Wünsche ohne Feld (Lücke im Modell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Feld</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Facetten</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Begründung</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>items.totals.tax</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Tax amount per line. v3 states only taxRate and effectiveTaxRate on a line — no money figure — so the tax a position carries cannot be read. The core will not derive it from gross minus net: that is a number Xentral never stated, and line-level rounding against the legacy PDF (projekt.preisberechnung) is still an open decision, so a derived value could silently disagree with the printed document. Per-rate tax exists on the document totals; the line needs its own.</t>
         </is>
       </c>
     </row>
@@ -78938,9 +79296,9 @@
           <t>Best-practice one-step return: create a return directly from a delivery note (the goods that were shipped). Provide the delivery note id and the lines to return — each with the delivery-note line item id, the quantity, and a REQUIRED ReturnReason id (list them via the ReturnReason entity).</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -78990,9 +79348,9 @@
           <t>Settle the return by issuing a credit note (Gutschrift) for the returned goods — the return's financial resolution. Optional command {isApproved, isPaid} (both default: approved, unpaid). A still-unreleased (draft) return is released first: a credit note issued from a draft leaves the return without a document number and it can never be released afterwards. The created credit note is linked on the return under `resolution.creditNote`.</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -79086,9 +79444,9 @@
           <t>Add a tag to this record (created automatically if new).</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -79110,9 +79468,9 @@
           <t>Remove a tag from this record.</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -79169,9 +79527,9 @@
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -79237,9 +79595,9 @@
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -79257,9 +79615,9 @@
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -81764,14 +82122,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -81795,7 +82153,11 @@
           <t>Tax rate applied to the line (e.g. 19).</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>create: Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream. | update: Deviating tax rate per position. Upstream derives the line tax from the product's tax class and the customer's tax rule; v3 accepts taxRate on a line item, answers 2xx and keeps its own value — measured on mvp 2026-08-01 (sent "reduced", read back "standard", on create and on update alike). Needs a real write path upstream.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -83389,9 +83751,9 @@
           <t>Send the purchase order to the supplier (v3 send — mails the document).</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -83557,9 +83919,9 @@
           <t>Add a tag to this record (created automatically if new).</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -83581,9 +83943,9 @@
           <t>Remove a tag from this record.</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -83640,9 +84002,9 @@
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -83660,9 +84022,9 @@
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -83680,9 +84042,9 @@
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -34269,7 +34269,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>No conversion endpoint in the public API — v1 salesOrders/import is a raw import, not a quote conversion.</t>
+          <t>No conversion endpoint we can reach. v3 has createFromSalesOrder and createFromDeliveryNote for invoices and returns, but no createFromOffer for sales orders, and POST /v3/salesOrders cannot reference a quote (the relation is read-only). v1 salesOrders/import is a raw import, not a conversion. The logic exists — Erpapi::WeiterfuehrenAngebotZuAuftrag copies the document and sets the quote to commissioned — and is exposed once, as the legacy XML API /api/v1/AngebotZuAuftrag. That one is digest-authenticated, hangs on a legacy permission and already sits behind a killswitch, so it is not usable from a bearer-token core.</t>
         </is>
       </c>
     </row>
@@ -34293,7 +34293,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>No duplicate endpoint upstream.</t>
+          <t>No duplicate endpoint in any API generation — no v3 action, nothing in v1/v2, nothing in the legacy XML API. erpAPI::CopyAngebot() does the work behind the UI only. The same function exists for orders, invoices and delivery notes, so one uniform actions/duplicate would serve every document type at once.</t>
         </is>
       </c>
     </row>
@@ -34317,7 +34317,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>No public PDF render endpoint; the archived files at /api/v2/{type}/{id}/files are not yet composed.</t>
+          <t>Not an upstream gap any more, a build task on our side: GET /api/v3/{document}/{id} with Accept: application/pdf renders the document (documented content negotiation, scope &lt;document&gt;:read; measured on mvp 2026-08-01 for offers, salesOrders, invoices, creditNotes, deliveryNotes and purchaseOrders). What is missing is the way back: the agent surface answers JSON, so the action has to hand the PDF over as a file reference. Note the render serves the archived copy when one exists (written on send / write protection), otherwise it renders fresh; the archived VERSIONS themselves have no API at all. /api/v2/{document}/{id}/files does exist but lists attachments, not the generated document.</t>
         </is>
       </c>
     </row>
@@ -34448,7 +34448,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Quote acceptance has no upstream endpoint — the v3 offers API only offers send/release/cancel.</t>
+          <t>No upstream endpoint. v3 offers has exactly release, cancel, send, logActivity, setWriteProtection and removeWriteProtection; UpdateOfferData carries no status, and offers do not exist in v1/v2 at all. The transition happens only in the UI. Worth settling first: the status 'accepted' (angenommen) is written by no code path and occurs in no tenant — the state the ERP really keeps is 'commissioned' (beauftragt), reached as a side effect of converting the quote into a sales order.</t>
         </is>
       </c>
     </row>
@@ -34472,7 +34472,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Quote decline has no upstream endpoint.</t>
+          <t>No upstream endpoint. Declining sets angebot.status='abgelehnt' and closes open follow-ups — two SQL updates inside the legacy page controller, with no service class, no API route and no event. The legacy XML API cannot reach it either: ApiBelegEdit whitelists the status values and 'abgelehnt' is not among them.</t>
         </is>
       </c>
     </row>
@@ -52990,7 +52990,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>No public PDF render endpoint; the archived files at /api/v2/{type}/{id}/files are not yet composed.</t>
+          <t>Not an upstream gap any more, a build task on our side: GET /api/v3/{document}/{id} with Accept: application/pdf renders the document (documented content negotiation, scope &lt;document&gt;:read; measured on mvp 2026-08-01 for offers, salesOrders, invoices, creditNotes, deliveryNotes and purchaseOrders). What is missing is the way back: the agent surface answers JSON, so the action has to hand the PDF over as a file reference. Note the render serves the archived copy when one exists (written on send / write protection), otherwise it renders fresh; the archived VERSIONS themselves have no API at all. /api/v2/{document}/{id}/files does exist but lists attachments, not the generated document.</t>
         </is>
       </c>
     </row>
@@ -64336,7 +64336,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>No public PDF render endpoint; the archived files at /api/v2/{type}/{id}/files are not yet composed.</t>
+          <t>Not an upstream gap any more, a build task on our side: GET /api/v3/{document}/{id} with Accept: application/pdf renders the document (documented content negotiation, scope &lt;document&gt;:read; measured on mvp 2026-08-01 for offers, salesOrders, invoices, creditNotes, deliveryNotes and purchaseOrders). What is missing is the way back: the agent surface answers JSON, so the action has to hand the PDF over as a file reference. Note the render serves the archived copy when one exists (written on send / write protection), otherwise it renders fresh; the archived VERSIONS themselves have no API at all. /api/v2/{document}/{id}/files does exist but lists attachments, not the generated document.</t>
         </is>
       </c>
     </row>
@@ -72244,7 +72244,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>No public PDF render endpoint; the archived files at /api/v2/{type}/{id}/files are not yet composed.</t>
+          <t>Not an upstream gap any more, a build task on our side: GET /api/v3/{document}/{id} with Accept: application/pdf renders the document (documented content negotiation, scope &lt;document&gt;:read; measured on mvp 2026-08-01 for offers, salesOrders, invoices, creditNotes, deliveryNotes and purchaseOrders). What is missing is the way back: the agent surface answers JSON, so the action has to hand the PDF over as a file reference. Note the render serves the archived copy when one exists (written on send / write protection), otherwise it renders fresh; the archived VERSIONS themselves have no API at all. /api/v2/{document}/{id}/files does exist but lists attachments, not the generated document.</t>
         </is>
       </c>
     </row>
@@ -76319,7 +76319,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>No public PDF render endpoint; the archived files at /api/v2/{type}/{id}/files are not yet composed.</t>
+          <t>Not an upstream gap any more, a build task on our side: GET /api/v3/{document}/{id} with Accept: application/pdf renders the document (documented content negotiation, scope &lt;document&gt;:read; measured on mvp 2026-08-01 for offers, salesOrders, invoices, creditNotes, deliveryNotes and purchaseOrders). What is missing is the way back: the agent surface answers JSON, so the action has to hand the PDF over as a file reference. Note the render serves the archived copy when one exists (written on send / write protection), otherwise it renders fresh; the archived VERSIONS themselves have no API at all. /api/v2/{document}/{id}/files does exist but lists attachments, not the generated document.</t>
         </is>
       </c>
     </row>
@@ -79423,7 +79423,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>No public PDF render endpoint; the archived files at /api/v2/{type}/{id}/files are not yet composed.</t>
+          <t>Not an upstream gap any more, a build task on our side: GET /api/v3/{document}/{id} with Accept: application/pdf renders the document (documented content negotiation, scope &lt;document&gt;:read; measured on mvp 2026-08-01 for offers, salesOrders, invoices, creditNotes, deliveryNotes and purchaseOrders). What is missing is the way back: the agent surface answers JSON, so the action has to hand the PDF over as a file reference. Note the render serves the archived copy when one exists (written on send / write protection), otherwise it renders fresh; the archived VERSIONS themselves have no API at all. /api/v2/{document}/{id}/files does exist but lists attachments, not the generated document.</t>
         </is>
       </c>
     </row>
@@ -83898,7 +83898,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>No public PDF render endpoint; the archived files at /api/v2/{type}/{id}/files are not yet composed.</t>
+          <t>Not an upstream gap any more, a build task on our side: GET /api/v3/{document}/{id} with Accept: application/pdf renders the document (documented content negotiation, scope &lt;document&gt;:read; measured on mvp 2026-08-01 for offers, salesOrders, invoices, creditNotes, deliveryNotes and purchaseOrders). What is missing is the way back: the agent surface answers JSON, so the action has to hand the PDF over as a file reference. Note the render serves the archived copy when one exists (written on send / write protection), otherwise it renders fresh; the archived VERSIONS themselves have no API at all. /api/v2/{document}/{id}/files does exist but lists attachments, not the generated document.</t>
         </is>
       </c>
     </row>

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -590,7 +590,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>verified.json zuletzt geschrieben: 2026-08-01 16:21</t>
+          <t>verified.json zuletzt geschrieben: 2026-08-01 18:00</t>
         </is>
       </c>
     </row>

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -590,7 +590,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>verified.json zuletzt geschrieben: 2026-08-01 18:00</t>
+          <t>verified.json zuletzt geschrieben: 2026-08-01 18:30</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6 (3/0)</t>
+          <t>6 (4/0)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7 (4/0)</t>
+          <t>7 (5/0)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>9 (3/0)</t>
+          <t>9 (4/0)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6 (3/0)</t>
+          <t>6 (4/0)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8 (4/0)</t>
+          <t>8 (5/0)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8 (3/0)</t>
+          <t>8 (4/0)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>13 (6/0)</t>
+          <t>13 (7/0)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -34309,17 +34309,17 @@
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Not an upstream gap any more, a build task on our side: GET /api/v3/{document}/{id} with Accept: application/pdf renders the document (documented content negotiation, scope &lt;document&gt;:read; measured on mvp 2026-08-01 for offers, salesOrders, invoices, creditNotes, deliveryNotes and purchaseOrders). What is missing is the way back: the agent surface answers JSON, so the action has to hand the PDF over as a file reference. Note the render serves the archived copy when one exists (written on send / write protection), otherwise it renders fresh; the archived VERSIONS themselves have no API at all. /api/v2/{document}/{id}/files does exist but lists attachments, not the generated document.</t>
-        </is>
-      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Fetch the rendered document as a PDF file. Upstream serves the archived copy when one exists (written on send and on write protection) and renders fresh otherwise. Returns the bytes as result.file (base64) — hand it to a file store rather than reading it.</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -52982,17 +52982,17 @@
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Not an upstream gap any more, a build task on our side: GET /api/v3/{document}/{id} with Accept: application/pdf renders the document (documented content negotiation, scope &lt;document&gt;:read; measured on mvp 2026-08-01 for offers, salesOrders, invoices, creditNotes, deliveryNotes and purchaseOrders). What is missing is the way back: the agent surface answers JSON, so the action has to hand the PDF over as a file reference. Note the render serves the archived copy when one exists (written on send / write protection), otherwise it renders fresh; the archived VERSIONS themselves have no API at all. /api/v2/{document}/{id}/files does exist but lists attachments, not the generated document.</t>
-        </is>
-      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Fetch the rendered document as a PDF file. Upstream serves the archived copy when one exists (written on send and on write protection) and renders fresh otherwise. Returns the bytes as result.file (base64) — hand it to a file store rather than reading it.</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -64328,17 +64328,17 @@
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Not an upstream gap any more, a build task on our side: GET /api/v3/{document}/{id} with Accept: application/pdf renders the document (documented content negotiation, scope &lt;document&gt;:read; measured on mvp 2026-08-01 for offers, salesOrders, invoices, creditNotes, deliveryNotes and purchaseOrders). What is missing is the way back: the agent surface answers JSON, so the action has to hand the PDF over as a file reference. Note the render serves the archived copy when one exists (written on send / write protection), otherwise it renders fresh; the archived VERSIONS themselves have no API at all. /api/v2/{document}/{id}/files does exist but lists attachments, not the generated document.</t>
-        </is>
-      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Fetch the rendered document as a PDF file. Upstream serves the archived copy when one exists (written on send and on write protection) and renders fresh otherwise. Returns the bytes as result.file (base64) — hand it to a file store rather than reading it.</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -72236,17 +72236,17 @@
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Not an upstream gap any more, a build task on our side: GET /api/v3/{document}/{id} with Accept: application/pdf renders the document (documented content negotiation, scope &lt;document&gt;:read; measured on mvp 2026-08-01 for offers, salesOrders, invoices, creditNotes, deliveryNotes and purchaseOrders). What is missing is the way back: the agent surface answers JSON, so the action has to hand the PDF over as a file reference. Note the render serves the archived copy when one exists (written on send / write protection), otherwise it renders fresh; the archived VERSIONS themselves have no API at all. /api/v2/{document}/{id}/files does exist but lists attachments, not the generated document.</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Fetch the rendered document as a PDF file. Upstream serves the archived copy when one exists (written on send and on write protection) and renders fresh otherwise. Returns the bytes as result.file (base64) — hand it to a file store rather than reading it.</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -76311,17 +76311,17 @@
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Not an upstream gap any more, a build task on our side: GET /api/v3/{document}/{id} with Accept: application/pdf renders the document (documented content negotiation, scope &lt;document&gt;:read; measured on mvp 2026-08-01 for offers, salesOrders, invoices, creditNotes, deliveryNotes and purchaseOrders). What is missing is the way back: the agent surface answers JSON, so the action has to hand the PDF over as a file reference. Note the render serves the archived copy when one exists (written on send / write protection), otherwise it renders fresh; the archived VERSIONS themselves have no API at all. /api/v2/{document}/{id}/files does exist but lists attachments, not the generated document.</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Fetch the rendered document as a PDF file. Upstream serves the archived copy when one exists (written on send and on write protection) and renders fresh otherwise. Returns the bytes as result.file (base64) — hand it to a file store rather than reading it.</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -79415,17 +79415,17 @@
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Not an upstream gap any more, a build task on our side: GET /api/v3/{document}/{id} with Accept: application/pdf renders the document (documented content negotiation, scope &lt;document&gt;:read; measured on mvp 2026-08-01 for offers, salesOrders, invoices, creditNotes, deliveryNotes and purchaseOrders). What is missing is the way back: the agent surface answers JSON, so the action has to hand the PDF over as a file reference. Note the render serves the archived copy when one exists (written on send / write protection), otherwise it renders fresh; the archived VERSIONS themselves have no API at all. /api/v2/{document}/{id}/files does exist but lists attachments, not the generated document.</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Fetch the rendered document as a PDF file. Upstream serves the archived copy when one exists (written on send and on write protection) and renders fresh otherwise. Returns the bytes as result.file (base64) — hand it to a file store rather than reading it.</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -83890,17 +83890,17 @@
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Not an upstream gap any more, a build task on our side: GET /api/v3/{document}/{id} with Accept: application/pdf renders the document (documented content negotiation, scope &lt;document&gt;:read; measured on mvp 2026-08-01 for offers, salesOrders, invoices, creditNotes, deliveryNotes and purchaseOrders). What is missing is the way back: the agent surface answers JSON, so the action has to hand the PDF over as a file reference. Note the render serves the archived copy when one exists (written on send / write protection), otherwise it renders fresh; the archived VERSIONS themselves have no API at all. /api/v2/{document}/{id}/files does exist but lists attachments, not the generated document.</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Fetch the rendered document as a PDF file. Upstream serves the archived copy when one exists (written on send and on write protection) and renders fresh otherwise. Returns the bytes as result.file (base64) — hand it to a file store rather than reading it.</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -571,6 +571,8 @@
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -590,7 +592,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>verified.json zuletzt geschrieben: 2026-08-02 09:10</t>
+          <t>Lauf beendet: 2026-08-02 07:21</t>
         </is>
       </c>
     </row>
@@ -652,6 +654,16 @@
           <t>Steps (ok/Fehler)</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>gemessen</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Actions gemessen</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -692,6 +704,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -732,6 +750,8 @@
           <t>2 (0/0)</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -772,6 +792,12 @@
           <t>2 (0/0)</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:32</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -812,6 +838,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -852,6 +884,16 @@
           <t>2 (1/0)</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:30</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -892,6 +934,16 @@
           <t>2 (0/0)</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:20</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -932,6 +984,16 @@
           <t>4 (3/0)</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:29</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -972,6 +1034,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1012,6 +1080,16 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1052,6 +1130,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1092,6 +1176,12 @@
           <t>2 (0/0)</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:31</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1132,6 +1222,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1172,6 +1268,8 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1212,6 +1310,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1252,6 +1356,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1292,6 +1402,12 @@
           <t>5 (0/0)</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1332,6 +1448,12 @@
           <t>2 (0/0)</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:34</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1372,6 +1494,16 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1388,13 +1520,13 @@
         <v>98</v>
       </c>
       <c r="D25" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G25" t="n">
         <v>373</v>
@@ -1412,6 +1544,12 @@
           <t>3 (0/0)</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:34</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1452,6 +1590,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1492,6 +1636,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1532,6 +1682,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1572,6 +1728,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1612,6 +1774,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1652,6 +1820,12 @@
           <t>2 (0/0)</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:31</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1692,6 +1866,16 @@
           <t>3 (3/0)</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:31</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1732,6 +1916,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1772,6 +1962,16 @@
           <t>4 (2/0)</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:26</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1812,6 +2012,16 @@
           <t>5 (3/0)</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:30</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1852,6 +2062,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1892,6 +2108,16 @@
           <t>2 (2/0)</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:28</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1932,6 +2158,16 @@
           <t>4 (4/0)</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:27</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1972,6 +2208,8 @@
           <t>2 (0/0)</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2012,6 +2250,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2052,6 +2296,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2092,6 +2342,8 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2132,6 +2384,8 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2172,6 +2426,12 @@
           <t>4 (0/0)</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2212,6 +2472,16 @@
           <t>2 (0/0)</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2252,6 +2522,16 @@
           <t>2 (0/0)</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-08-02 07:21</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2292,6 +2572,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2332,6 +2618,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2372,6 +2664,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2412,6 +2710,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2452,6 +2756,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2492,6 +2802,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2532,6 +2848,12 @@
           <t>0 (0/0)</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-08-02 06:35</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:J53"/>
@@ -2575,6 +2897,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:31</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -5942,6 +6269,11 @@
           <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 07:20</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -10881,6 +11213,11 @@
           <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 07:21</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -15876,6 +16213,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:32</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -16983,6 +17325,11 @@
           <t>Operations: list, read, create, update</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:34</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -18185,9 +18532,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -18206,11 +18553,7 @@
           <t>EAN / GTIN barcode of the product.</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed | search: probed with a fixture value — no sampled record carries this field</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -18459,9 +18802,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -18480,11 +18823,7 @@
           <t>Manufacturer's own article number (MPN).</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -19686,7 +20025,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>create: created prd_61996 (labelled 'VT Verify') — no delete endpoint, left in place</t>
+          <t>create: created prd_61997 (labelled 'VT Verify') — no delete endpoint, left in place</t>
         </is>
       </c>
     </row>
@@ -22832,6 +23171,11 @@
           <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:34</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -24307,6 +24651,11 @@
           <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -25369,6 +25718,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -30013,6 +30367,11 @@
           <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -34879,6 +35238,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -37469,6 +37833,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -39634,6 +40003,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -43575,6 +43949,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -44208,6 +44587,11 @@
           <t>Operations: list, read, create</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -44881,6 +45265,11 @@
           <t>Operations: list</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -45722,6 +46111,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -46362,6 +46756,11 @@
           <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:27</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -53580,6 +53979,11 @@
           <t>Operations: list</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -54046,6 +54450,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -54714,6 +55123,11 @@
           <t>Operations: list</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -55220,6 +55634,11 @@
           <t>Operations: list</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -55574,6 +55993,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -56345,6 +56769,11 @@
           <t>Operations: list</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -57061,6 +57490,11 @@
           <t>Operations: list</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -57469,6 +57903,11 @@
           <t>Operations: list</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -58338,6 +58777,11 @@
           <t>Operations: list</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -59055,6 +59499,11 @@
           <t>Operations: list</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -59512,6 +59961,11 @@
           <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:28</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -64882,6 +65336,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -65290,6 +65749,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -65801,6 +66265,11 @@
           <t>Operations: list</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -66204,6 +66673,11 @@
           <t>Operations: list</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -66612,6 +67086,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -66971,6 +67450,11 @@
           <t>Operations: list</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -67531,6 +68015,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -68042,6 +68531,11 @@
           <t>Operations: list</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -68401,6 +68895,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:35</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -68922,6 +69421,11 @@
           <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:29</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -72775,6 +73279,11 @@
           <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:30</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -76837,6 +77346,11 @@
           <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:30</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -79954,6 +80468,11 @@
           <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:31</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -84381,6 +84900,11 @@
           <t>Operations: list, read</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>gemessen: 2026-08-02 06:31</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -68,7 +68,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'GoodsReceipt'!$A$4:$L$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'PurchaseInvoice'!$A$4:$L$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Customer'!$A$4:$L$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Supplier'!$A$4:$L$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Supplier'!$A$4:$L$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Channel'!$A$4:$L$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Product'!$A$4:$L$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'PriceList'!$A$4:$L$26</definedName>
@@ -590,7 +590,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>verified.json zuletzt geschrieben: 2026-08-01 18:30</t>
+          <t>verified.json zuletzt geschrieben: 2026-08-02 09:10</t>
         </is>
       </c>
     </row>
@@ -2225,19 +2225,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D46" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G46" t="n">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="H46" t="n">
         <v>33</v>
@@ -10851,7 +10851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -10878,7 +10878,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Operations: list, read, create, update</t>
+          <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
     </row>
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -13077,17 +13077,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>defaults</t>
+          <t>customFields.key</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Defaults</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -13095,14 +13095,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -13121,17 +13121,12 @@
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Default commercial terms for purchasing from this supplier.</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>defaults.currency</t>
+          <t>customFields.label</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -13141,7 +13136,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -13149,14 +13144,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -13175,17 +13170,12 @@
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Default currency for the supplier's documents.</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>defaults.language</t>
+          <t>customFields.type</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -13195,7 +13185,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -13234,32 +13224,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>defaults.partialShipping</t>
+          <t>customFields.value</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Partial shipping</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -13278,26 +13268,22 @@
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>read: The partial-shipping preference is not surfaced by the v3 partner read. | update: The partial-shipping preference is not surfaced by the v3 partner read.</t>
-        </is>
-      </c>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>defaults.paymentMethod</t>
+          <t>defaults</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Payment method</t>
+          <t>Defaults</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -13333,7 +13319,7 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Default payment method for the supplier.</t>
+          <t>Default commercial terms for purchasing from this supplier.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -13341,17 +13327,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>defaults.paymentTerms</t>
+          <t>defaults.currency</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Payment terms</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -13387,7 +13373,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Default payment terms towards the supplier.</t>
+          <t>Default currency for the supplier's documents.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -13395,17 +13381,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>defaults.paymentTerms.discountDays</t>
+          <t>defaults.language</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Discount days</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -13444,22 +13430,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>defaults.paymentTerms.discountPercent</t>
+          <t>defaults.partialShipping</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Discount %</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>Partial shipping</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -13467,9 +13453,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -13488,22 +13474,26 @@
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>read: The partial-shipping preference is not surfaced by the v3 partner read. | update: The partial-shipping preference is not surfaced by the v3 partner read.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>defaults.paymentTerms.dueDays</t>
+          <t>defaults.paymentMethod</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Due days</t>
+          <t>Payment method</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -13511,14 +13501,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -13537,31 +13527,32 @@
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>create: Default supplier payment term — drives liability due dates. | update: Default supplier payment term — drives liability due dates.</t>
-        </is>
-      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Default payment method for the supplier.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>defaults.priceList</t>
+          <t>defaults.paymentTerms</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Price list</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+          <t>Payment terms</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -13569,9 +13560,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -13590,31 +13581,32 @@
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>read: The assigned price list is not surfaced by the v3 partner read. | update: The assigned price list is not surfaced by the v3 partner read.</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Default payment terms towards the supplier.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>defaults.shippingMethod</t>
+          <t>defaults.paymentTerms.discountDays</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Shipping method</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+          <t>Discount days</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -13622,9 +13614,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -13643,26 +13635,22 @@
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>read: The default shipping method is not surfaced by the v3 partner read. | update: The default shipping method is not surfaced by the v3 partner read.</t>
-        </is>
-      </c>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>defaults.paymentTerms.discountPercent</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Discount %</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -13670,19 +13658,19 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -13690,33 +13678,28 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Primary email of the supplier.</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>defaults.paymentTerms.dueDays</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Due days</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -13724,14 +13707,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -13750,32 +13733,31 @@
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Read-only financial standing of the supplier (A/P).</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>create: Default supplier payment term — drives liability due dates. | update: Default supplier payment term — drives liability due dates.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>finance.creditorAccountNumber</t>
+          <t>defaults.priceList</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Creditor account</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>Price list</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -13804,31 +13786,26 @@
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Deviating creditor (A/P) account for the bookkeeping / DATEV export.</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>update: The creditor account for the FiBu/DATEV export — settable per supplier.</t>
+          <t>read: The assigned price list is not surfaced by the v3 partner read. | update: The assigned price list is not surfaced by the v3 partner read.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>finance.openAmount</t>
+          <t>defaults.shippingMethod</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Open amount</t>
+          <t>Shipping method</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -13841,9 +13818,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -13862,21 +13839,16 @@
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Total currently unpaid amount (open liabilities) towards this supplier.</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>read: Aggregated open liabilities per supplier are computed nowhere in the API — must be derived/served.</t>
+          <t>read: The default shipping method is not surfaced by the v3 partner read. | update: The default shipping method is not surfaced by the v3 partner read.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>finance.openAmount.amount</t>
+          <t>email</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -13886,7 +13858,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -13894,19 +13866,19 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -13914,28 +13886,33 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Primary email of the supplier.</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>finance.openAmount.currency</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -13969,12 +13946,17 @@
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Read-only financial standing of the supplier (A/P).</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>finance.creditorAccountNumber</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -13984,7 +13966,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Creditor account</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -13997,9 +13979,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -14020,25 +14002,29 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>The record's stable, unique identifier — use it to read, link (references) and write this record. A typed 'speaking' id (e.g. cus_4711); assigned automatically when the record is created.</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
+          <t>Deviating creditor (A/P) account for the bookkeeping / DATEV export.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>update: The creditor account for the FiBu/DATEV export — settable per supplier.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>finance.onHold</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>On hold</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -14046,14 +14032,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -14072,75 +14058,70 @@
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Preferred correspondence language.</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>finance.openAmount</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>Open amount</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Supplier / company name (the main address name).</t>
+          <t>Total currently unpaid amount (open liabilities) towards this supplier.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>create: created sup_20462 but DELETE returned 405 — manual cleanup needed (record is named 'VT Verify GmbH')</t>
+          <t>read: Aggregated open liabilities per supplier are computed nowhere in the API — must be derived/served.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>finance.openAmount.amount</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -14150,7 +14131,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -14168,33 +14149,28 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Human-facing supplier number (e.g. 70001).</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>finance.openAmount.currency</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -14204,7 +14180,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -14238,32 +14214,27 @@
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Type discriminator of the record (its entity name).</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Parent (HQ)</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -14271,9 +14242,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -14294,19 +14265,15 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Parent company in a branch → HQ hierarchy: this record is a branch of the referenced supplier.</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>read: B2B hierarchy (branch → HQ) is not exposed via the public API (plan §6.1 parent). | update: B2B hierarchy (branch → HQ) is not exposed via the public API (plan §6.1 parent).</t>
-        </is>
-      </c>
+          <t>The record's stable, unique identifier — use it to read, link (references) and write this record. A typed 'speaking' id (e.g. cus_4711); assigned automatically when the record is created.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>language</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -14316,7 +14283,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -14352,7 +14319,7 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Primary phone of the supplier.</t>
+          <t>Preferred correspondence language.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -14360,17 +14327,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Main project</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -14378,9 +14345,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -14388,47 +14355,43 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Main project this supplier is assigned to.</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>update: only one project on the instance — write accepted, change not provable</t>
-        </is>
-      </c>
+          <t>Supplier / company name (the main address name).</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>purchasing</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Purchasing</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -14436,14 +14399,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -14462,27 +14425,22 @@
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Supplier-specific purchasing defaults.</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>purchasing.confirmationRequired</t>
+          <t>number</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Confirmation required</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -14490,57 +14448,53 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Whether an order confirmation (AB) is required from this supplier.</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>create: Whether an order confirmation (AB) is required from this supplier — drives purchasing workflow; not settable via API today. | update: Whether an order confirmation (AB) is required from this supplier — drives purchasing workflow; not settable via API today.</t>
-        </is>
-      </c>
+          <t>Human-facing supplier number (e.g. 70001).</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>purchasing.deliveryDays</t>
+          <t>object</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Delivery days</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -14548,14 +14502,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -14576,34 +14530,30 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Standard supplier lead time in days (feeds replenishment planning).</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>create: Standard supplier lead time in days — feeds replenishment planning. | update: Standard supplier lead time in days — feeds replenishment planning.</t>
-        </is>
-      </c>
+          <t>Type discriminator of the record (its entity name).</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>purchasing.minimumOrderValue</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Minimum order value</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>Parent (HQ)</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -14611,9 +14561,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -14634,15 +14584,19 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Minimum order value the supplier requires.</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
+          <t>Parent company in a branch → HQ hierarchy: this record is a branch of the referenced supplier.</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>read: B2B hierarchy (branch → HQ) is not exposed via the public API (plan §6.1 parent). | update: B2B hierarchy (branch → HQ) is not exposed via the public API (plan §6.1 parent).</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>purchasing.minimumOrderValue.amount</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -14652,7 +14606,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -14660,14 +14614,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -14686,22 +14640,27 @@
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Primary phone of the supplier.</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>purchasing.minimumOrderValue.currency</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Main project</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -14709,14 +14668,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -14735,22 +14694,31 @@
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Main project this supplier is assigned to.</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>update: only one project on the instance — write accepted, change not provable</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>purchasing.ourCustomerNumber</t>
+          <t>purchasing</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Our customer number</t>
+          <t>Purchasing</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -14758,14 +14726,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -14786,7 +14754,7 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Our customer number AT the supplier — how they identify us on their side.</t>
+          <t>Supplier-specific purchasing defaults.</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -14794,17 +14762,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>purchasing.sendOrdersVia</t>
+          <t>purchasing.confirmationRequired</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Send orders via</t>
+          <t>Confirmation required</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -14840,39 +14808,39 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>How purchase orders are sent to the supplier (email / portal / EDI).</t>
+          <t>Whether an order confirmation (AB) is required from this supplier.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>create: How POs are sent to the supplier (email/portal/EDI) — a supplier default that must be settable. | update: How POs are sent to the supplier (email/portal/EDI) — a supplier default that must be settable.</t>
+          <t>create: Whether an order confirmation (AB) is required from this supplier — drives purchasing workflow; not settable via API today. | update: Whether an order confirmation (AB) is required from this supplier — drives purchasing workflow; not settable via API today.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>purchasing.deliveryDays</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
+          <t>Delivery days</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -14898,29 +14866,29 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Lifecycle state of the supplier: active or archived.</t>
+          <t>Standard supplier lead time in days (feeds replenishment planning).</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>read: Active/archived state is not exposed via v3 suppliers — needed for honest archiving (plan §6.1). | update: Active/archived state is not exposed via v3 suppliers — needed for honest archiving (plan §6.1).</t>
+          <t>create: Standard supplier lead time in days — feeds replenishment planning. | update: Standard supplier lead time in days — feeds replenishment planning.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>purchasing.minimumOrderValue</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>tag</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>Minimum order value</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -14928,19 +14896,19 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -14956,7 +14924,7 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Free-text labels for grouping/segmenting the record.</t>
+          <t>Minimum order value the supplier requires.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -14964,17 +14932,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>purchasing.minimumOrderValue.amount</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -15008,27 +14976,22 @@
         </is>
       </c>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Kind of partner: person or company (salutation / legal form) — not the customer/supplier role.</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>updatedAt</t>
+          <t>purchasing.minimumOrderValue.currency</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Updated at</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -15046,14 +15009,14 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G80" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -15062,17 +15025,12 @@
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Timestamp the record was last changed.</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>vatId</t>
+          <t>purchasing.ourCustomerNumber</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -15082,7 +15040,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>VAT id</t>
+          <t>Our customer number</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -15090,9 +15048,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -15118,7 +15076,7 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>VAT identification number (USt-IdNr.) for tax / reverse-charge handling.</t>
+          <t>Our customer number AT the supplier — how they identify us on their side.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -15126,17 +15084,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>purchasing.sendOrdersVia</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>select</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Send orders via</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -15144,14 +15102,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -15172,266 +15130,487 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Supplier's website.</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
+          <t>How purchase orders are sent to the supplier (email / portal / EDI).</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>create: How POs are sent to the supplier (email/portal/EDI) — a supplier default that must be settable. | update: How POs are sent to the supplier (email/portal/EDI) — a supplier default that must be settable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Lifecycle state of the supplier: active or archived.</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>read: Active/archived state is not exposed via v3 suppliers — needed for honest archiving (plan §6.1). | update: Active/archived state is not exposed via v3 suppliers — needed for honest archiving (plan §6.1).</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="inlineStr">
-        <is>
-          <t>Actions</t>
-        </is>
-      </c>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Free-text labels for grouping/segmenting the record.</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>destruktiv</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Beschreibung</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>Notiz</t>
-        </is>
-      </c>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Kind of partner: person or company (salutation / legal form) — not the customer/supplier role.</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>setHold</t>
+          <t>updatedAt</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Set hold</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Supplier holds are not writable via the public API.</t>
-        </is>
-      </c>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Updated at</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Timestamp the record was last changed.</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>releaseHold</t>
+          <t>vatId</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Release hold</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Supplier holds are not writable via the public API.</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>VAT id</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>VAT identification number (USt-IdNr.) for tax / reverse-charge handling.</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mergeInto</t>
+          <t>website</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Merge into</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Duplicate merge is a UI-only feature — no API.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>runCreditCheck</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Run credit check</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Credit checks have no public trigger.</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Supplier's website.</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>statement</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Open-items statement</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>An open-items statement is not exposed via the public API.</t>
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>Actions</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>addTag</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Add tag</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Add a tag to this record (created automatically if new).</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>destruktiv</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Beschreibung</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Notiz</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>removeTag</t>
+          <t>setHold</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Remove tag</t>
+          <t>Set hold</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Remove a tag from this record.</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Supplier holds are not writable via the public API.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>releaseHold</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Release hold</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Supplier holds are not writable via the public API.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr">
-        <is>
-          <t>Process-Steps</t>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>mergeInto</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Merge into</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Duplicate merge is a UI-only feature — no API.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>destruktiv</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Beschreibung</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Notiz</t>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>runCreditCheck</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Run credit check</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Credit checks have no public trigger.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>archive</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Status › Archive</t>
+          <t>Open-items statement</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -15443,109 +15622,220 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>No archive flag is writable via v1 suppliers.</t>
+          <t>An open-items statement is not exposed via the public API.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>reactivate</t>
+          <t>addTag</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Status › Reactivate</t>
+          <t>Add tag</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>No archive flag is writable via v1 suppliers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="inlineStr">
-        <is>
-          <t>Wünsche ohne Feld (Lücke im Modell)</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Add a tag to this record (created automatically if new).</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>removeTag</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Remove tag</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Remove a tag from this record.</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>Feld</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Facetten</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>Process-Steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>destruktiv</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Beschreibung</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Begründung</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>contacts.address</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>create, read, update</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Notiz</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Status › Archive</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>No archive flag is writable via v1 suppliers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>reactivate</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Status › Reactivate</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>No archive flag is writable via v1 suppliers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>Wünsche ohne Feld (Lücke im Modell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Feld</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Facetten</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Begründung</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>contacts.address</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>create, read, update</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Bind a contact person to a specific address (person-at-location) — v3 stores only a free-text contactPerson on delivery addresses, not a reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>contacts.isPrimary</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>create, read, update</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>Mark the main contact person — v3 contactPersons carry no primary flag.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L82"/>
+  <autoFilter ref="A4:L88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -609,7 +609,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lauf beendet: 2026-08-02 09:52</t>
+          <t>Lauf beendet: 2026-08-02 10:27</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-08-02 09:49</t>
+          <t>2026-08-02 10:17</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -825,7 +825,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-08-02 09:46</t>
+          <t>2026-08-02 10:14</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -913,7 +913,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6 (2/0)</t>
+          <t>6 (3/0)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-08-02 09:42</t>
+          <t>2026-08-02 10:26</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2026-08-02 10:26</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-08-02 09:45</t>
+          <t>2026-08-02 10:13</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7 (2/0)</t>
+          <t>7 (3/0)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-08-02 09:41</t>
+          <t>2026-08-02 10:25</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2026-08-02 10:25</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-08-02 09:49</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-08-02 09:43</t>
+          <t>2026-08-02 10:12</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-08-02 09:49</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -1588,7 +1588,7 @@
         <v>98</v>
       </c>
       <c r="D25" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="E25" t="n">
         <v>34</v>
@@ -1597,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="H25" t="n">
         <v>373</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-08-02 09:47</t>
+          <t>2026-08-02 10:15</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-08-02 09:49</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-08-02 09:49</t>
+          <t>2026-08-02 10:17</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-08-02 09:49</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-08-02 09:49</t>
+          <t>2026-08-02 10:17</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-08-02 09:49</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-08-02 09:43</t>
+          <t>2026-08-02 10:12</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>9 (2/0)</t>
+          <t>9 (3/0)</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-08-02 09:43</t>
+          <t>2026-08-02 10:27</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2026-08-02 10:27</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>6 (2/0)</t>
+          <t>6 (3/0)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-08-02 09:37</t>
+          <t>2026-08-02 10:21</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2026-08-02 10:21</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8 (2/0)</t>
+          <t>8 (3/0)</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-08-02 09:42</t>
+          <t>2026-08-02 10:27</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2026-08-02 10:27</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8 (2/0)</t>
+          <t>8 (3/0)</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-08-02 09:40</t>
+          <t>2026-08-02 10:24</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2026-08-02 10:24</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>13 (2/0)</t>
+          <t>13 (3/0)</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-08-02 09:39</t>
+          <t>2026-08-02 10:23</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2026-08-02 10:23</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-08-02 09:52</t>
+          <t>2026-08-02 10:14</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-08-02 09:49</t>
+          <t>2026-08-02 10:17</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-08-02 09:49</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-08-02 09:48</t>
+          <t>2026-08-02 10:16</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-08-02 09:49</t>
+          <t>2026-08-02 10:17</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-08-02 09:49</t>
+          <t>2026-08-02 10:17</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:43</t>
+          <t>gemessen: 2026-08-02 10:12</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:45</t>
+          <t>gemessen: 2026-08-02 10:13</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:52</t>
+          <t>gemessen: 2026-08-02 10:14</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:46</t>
+          <t>gemessen: 2026-08-02 10:14</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:47</t>
+          <t>gemessen: 2026-08-02 10:15</t>
         </is>
       </c>
     </row>
@@ -18485,9 +18485,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -18593,9 +18593,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -18871,9 +18871,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -19157,9 +19157,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -19489,9 +19489,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -19651,9 +19651,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -19705,9 +19705,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -20215,9 +20215,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -20323,9 +20323,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -20377,9 +20377,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -20431,9 +20431,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>create: create not probed — no delete endpoint (net-zero impossible); set VERIFY_CREATE_NONZERO=1 to probe and leave a labelled record</t>
+          <t>create: created prd_61998 (labelled 'VT Verify') — no delete endpoint, left in place</t>
         </is>
       </c>
     </row>
@@ -20700,9 +20700,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -20928,9 +20928,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -21152,9 +21152,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -22701,9 +22701,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -22971,9 +22971,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -23025,9 +23025,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -23588,7 +23588,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -26183,7 +26183,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -30876,7 +30876,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:37</t>
+          <t>gemessen: 2026-08-02 10:21</t>
         </is>
       </c>
     </row>
@@ -35522,14 +35522,14 @@
           <t>Fetch the rendered document as a PDF file. Upstream serves the archived copy when one exists (written on send and on write protection) and renders fresh otherwise. Returns the bytes as result.file (base64) — hand it to a file store rather than reading it.</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>EXECUTED on the sampled record (200) — created/changed data</t>
+          <t>rendered Quote-100000.pdf (2253 bytes of real PDF) — read-only, net-zero</t>
         </is>
       </c>
     </row>
@@ -35648,7 +35648,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -35720,7 +35720,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -38494,7 +38494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -40716,7 +40716,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -44722,7 +44722,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -45360,7 +45360,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -46038,7 +46038,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -46888,7 +46888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -47537,7 +47537,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:39</t>
+          <t>gemessen: 2026-08-02 10:23</t>
         </is>
       </c>
     </row>
@@ -54619,14 +54619,14 @@
           <t>Fetch the rendered document as a PDF file. Upstream serves the archived copy when one exists (written on send and on write protection) and renders fresh otherwise. Returns the bytes as result.file (base64) — hand it to a file store rather than reading it.</t>
         </is>
       </c>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>EXECUTED on the sampled record (200) — created/changed data</t>
+          <t>rendered SalesOrder-200005.pdf (2225 bytes of real PDF) — read-only, net-zero</t>
         </is>
       </c>
     </row>
@@ -54777,7 +54777,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -54801,7 +54801,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -54825,7 +54825,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -54956,7 +54956,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -55427,7 +55427,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -56100,7 +56100,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -56611,7 +56611,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -56970,7 +56970,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -57762,7 +57762,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -58487,7 +58487,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:48</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -58900,7 +58900,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:49</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -59774,7 +59774,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:49</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -60496,7 +60496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:49</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -60958,7 +60958,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:40</t>
+          <t>gemessen: 2026-08-02 10:24</t>
         </is>
       </c>
     </row>
@@ -66160,14 +66160,14 @@
           <t>Fetch the rendered document as a PDF file. Upstream serves the archived copy when one exists (written on send and on write protection) and renders fresh otherwise. Returns the bytes as result.file (base64) — hand it to a file store rather than reading it.</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>EXECUTED on the sampled record (200) — created/changed data</t>
+          <t>rendered SalesInvoice-400002.pdf (2205 bytes of real PDF) — read-only, net-zero</t>
         </is>
       </c>
     </row>
@@ -66310,7 +66310,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -66342,7 +66342,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>EXECUTED on the sampled record (200) — created/changed data</t>
+          <t>EXECUTED on the sampled record (200) — effect not read back</t>
         </is>
       </c>
     </row>
@@ -66441,7 +66441,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:49</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -66854,7 +66854,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:49</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -67370,7 +67370,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:49</t>
+          <t>gemessen: 2026-08-02 10:16</t>
         </is>
       </c>
     </row>
@@ -67778,7 +67778,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:49</t>
+          <t>gemessen: 2026-08-02 10:17</t>
         </is>
       </c>
     </row>
@@ -68191,7 +68191,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:49</t>
+          <t>gemessen: 2026-08-02 10:17</t>
         </is>
       </c>
     </row>
@@ -68555,7 +68555,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:49</t>
+          <t>gemessen: 2026-08-02 10:17</t>
         </is>
       </c>
     </row>
@@ -69120,7 +69120,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:49</t>
+          <t>gemessen: 2026-08-02 10:17</t>
         </is>
       </c>
     </row>
@@ -69636,7 +69636,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:49</t>
+          <t>gemessen: 2026-08-02 10:17</t>
         </is>
       </c>
     </row>
@@ -70000,7 +70000,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:49</t>
+          <t>gemessen: 2026-08-02 10:17</t>
         </is>
       </c>
     </row>
@@ -70526,7 +70526,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:41</t>
+          <t>gemessen: 2026-08-02 10:25</t>
         </is>
       </c>
     </row>
@@ -74226,14 +74226,14 @@
           <t>Fetch the rendered document as a PDF file. Upstream serves the archived copy when one exists (written on send and on write protection) and renders fresh otherwise. Returns the bytes as result.file (base64) — hand it to a file store rather than reading it.</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>EXECUTED on the sampled record (200) — created/changed data</t>
+          <t>rendered DeliveryNote-300002.pdf (1950 bytes of real PDF) — read-only, net-zero</t>
         </is>
       </c>
     </row>
@@ -74376,7 +74376,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -74424,7 +74424,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -74448,7 +74448,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -74496,7 +74496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:42</t>
+          <t>gemessen: 2026-08-02 10:26</t>
         </is>
       </c>
     </row>
@@ -78366,14 +78366,14 @@
           <t>Fetch the rendered document as a PDF file. Upstream serves the archived copy when one exists (written on send and on write protection) and renders fresh otherwise. Returns the bytes as result.file (base64) — hand it to a file store rather than reading it.</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>EXECUTED on the sampled record (200) — created/changed data</t>
+          <t>rendered CreditNote-900000.pdf (1806 bytes of real PDF) — read-only, net-zero</t>
         </is>
       </c>
     </row>
@@ -78492,7 +78492,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -78615,7 +78615,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:42</t>
+          <t>gemessen: 2026-08-02 10:27</t>
         </is>
       </c>
     </row>
@@ -81527,14 +81527,14 @@
           <t>Fetch the rendered document as a PDF file. Upstream serves the archived copy when one exists (written on send and on write protection) and renders fresh otherwise. Returns the bytes as result.file (base64) — hand it to a file store rather than reading it.</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>EXECUTED on the sampled record (200) — created/changed data</t>
+          <t>rendered Return-500001.pdf (1990 bytes of real PDF) — read-only, net-zero</t>
         </is>
       </c>
     </row>
@@ -81653,7 +81653,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -81725,7 +81725,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -81749,7 +81749,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -81797,7 +81797,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:43</t>
+          <t>gemessen: 2026-08-02 10:27</t>
         </is>
       </c>
     </row>
@@ -86083,14 +86083,14 @@
           <t>Fetch the rendered document as a PDF file. Upstream serves the archived copy when one exists (written on send and on write protection) and renders fresh otherwise. Returns the bytes as result.file (base64) — hand it to a file store rather than reading it.</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>EXECUTED on the sampled record (200) — created/changed data</t>
+          <t>rendered PurchaseOrder-100000.pdf (2230 bytes of real PDF) — read-only, net-zero</t>
         </is>
       </c>
     </row>
@@ -86209,7 +86209,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -86233,7 +86233,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -86257,7 +86257,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>reachable — 409: Resource status invalid for requested operation</t>
+          <t>reachable — 409 from upstream: Resource status invalid for requested operation</t>
         </is>
       </c>
     </row>
@@ -86305,7 +86305,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 09:43</t>
+          <t>gemessen: 2026-08-02 10:12</t>
         </is>
       </c>
     </row>

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -130,7 +130,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -167,11 +167,6 @@
         <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4B183"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -185,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -204,9 +199,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -609,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lauf beendet: 2026-08-02 10:27</t>
+          <t>Lauf beendet: 2026-08-02 11:36</t>
         </is>
       </c>
     </row>
@@ -947,19 +939,19 @@
         <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E12" t="n">
         <v>25</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H12" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I12" t="n">
         <v>36</v>
@@ -976,7 +968,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-08-02 10:13</t>
+          <t>2026-08-02 11:35</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1588,13 +1580,13 @@
         <v>98</v>
       </c>
       <c r="D25" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E25" t="n">
         <v>34</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>45</v>
@@ -1617,7 +1609,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-08-02 10:15</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -1882,13 +1874,13 @@
         <v>56</v>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E31" t="n">
         <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1911,7 +1903,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-08-02 10:12</t>
+          <t>2026-08-02 10:59</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -2625,19 +2617,19 @@
         <v>84</v>
       </c>
       <c r="D46" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E46" t="n">
         <v>29</v>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H46" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I46" t="n">
         <v>33</v>
@@ -2654,7 +2646,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-08-02 10:14</t>
+          <t>2026-08-02 11:36</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3050,7 +3042,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:12</t>
+          <t>gemessen: 2026-08-02 10:59</t>
         </is>
       </c>
     </row>
@@ -5705,9 +5697,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -5716,11 +5708,7 @@
           <t>The invoice number printed on the supplier's document.</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>search: declared searchable, but not part of this entity's search fan-out — searchFields is empty, so a consolidated search never looks at this field</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6482,7 +6470,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:13</t>
+          <t>gemessen: 2026-08-02 11:35</t>
         </is>
       </c>
     </row>
@@ -6633,9 +6621,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -6643,9 +6631,9 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -6656,7 +6644,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -6745,9 +6733,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -6755,9 +6743,9 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -6768,7 +6756,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -7189,9 +7177,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -7199,9 +7187,9 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -7212,7 +7200,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -7247,9 +7235,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -7257,9 +7245,9 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -7270,7 +7258,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -7363,9 +7351,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -7373,9 +7361,9 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -7386,7 +7374,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:14</t>
+          <t>gemessen: 2026-08-02 11:36</t>
         </is>
       </c>
     </row>
@@ -11645,9 +11633,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -11655,9 +11643,9 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -11668,7 +11656,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -11757,9 +11745,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -11767,9 +11755,9 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -11780,7 +11768,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -12205,9 +12193,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -12215,9 +12203,9 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -12228,7 +12216,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -12263,9 +12251,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -12273,9 +12261,9 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -12286,7 +12274,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -12379,9 +12367,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -12389,9 +12377,9 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -12402,7 +12390,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17694,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:15</t>
+          <t>gemessen: 2026-08-02 11:13</t>
         </is>
       </c>
     </row>
@@ -18945,9 +18933,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -18956,11 +18944,7 @@
           <t>EAN / GTIN barcode of the product.</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>search: declared searchable, but not part of this entity's search fan-out — searchFields is ['name', 'number'], so a consolidated search never looks at this field</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -20464,7 +20448,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>create: created prd_61998 (labelled 'VT Verify') — no delete endpoint, left in place</t>
+          <t>create: created prd_61999 (labelled 'VT Verify') — no delete endpoint, left in place</t>
         </is>
       </c>
     </row>

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lauf beendet: 2026-08-02 11:36</t>
+          <t>Lauf beendet: 2026-08-02 12:15</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
         <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>264</v>
@@ -915,7 +915,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-08-02 10:26</t>
+          <t>2026-08-02 12:14</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -992,7 +992,7 @@
         <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E13" t="n">
         <v>25</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>253</v>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-08-02 10:25</t>
+          <t>2026-08-02 12:13</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1923,7 +1923,7 @@
         <v>73</v>
       </c>
       <c r="D32" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E32" t="n">
         <v>14</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>297</v>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-08-02 10:27</t>
+          <t>2026-08-02 12:15</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2025,16 +2025,16 @@
         <v>81</v>
       </c>
       <c r="D34" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
         <v>308</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-08-02 10:21</t>
+          <t>2026-08-02 12:09</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2078,7 +2078,7 @@
         <v>48</v>
       </c>
       <c r="D35" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E35" t="n">
         <v>11</v>
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
         <v>178</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-08-02 10:27</t>
+          <t>2026-08-02 12:14</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2180,7 +2180,7 @@
         <v>90</v>
       </c>
       <c r="D37" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E37" t="n">
         <v>26</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
         <v>367</v>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-08-02 10:24</t>
+          <t>2026-08-02 12:12</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2233,7 +2233,7 @@
         <v>121</v>
       </c>
       <c r="D38" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E38" t="n">
         <v>40</v>
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H38" t="n">
         <v>487</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-08-02 10:23</t>
+          <t>2026-08-02 12:11</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -6639,7 +6639,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>City / town.</t>
+          <t>City / town. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -6751,7 +6751,7 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ISO country code (e.g. DE).</t>
+          <t>ISO country code (e.g. DE). Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -7195,7 +7195,7 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>State / region / province.</t>
+          <t>State / region / province. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -7253,7 +7253,7 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Street and house number.</t>
+          <t>Street and house number. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -7369,7 +7369,7 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Postal code.</t>
+          <t>Postal code. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -11651,7 +11651,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>City / town.</t>
+          <t>City / town. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -11763,7 +11763,7 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ISO country code (e.g. DE).</t>
+          <t>ISO country code (e.g. DE). Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -12211,7 +12211,7 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>State / region / province.</t>
+          <t>State / region / province. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -12269,7 +12269,7 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Street and house number.</t>
+          <t>Street and house number. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -12385,7 +12385,7 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Postal code.</t>
+          <t>Postal code. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -30860,7 +30860,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:21</t>
+          <t>gemessen: 2026-08-02 12:09</t>
         </is>
       </c>
     </row>
@@ -32825,9 +32825,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -32846,11 +32846,7 @@
           <t>The quoted product.</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -34907,9 +34903,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -34928,11 +34924,7 @@
           <t>Free-text labels for grouping/segmenting the record.</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>filter: accepted, but the page does not contain the record the value came from — the filter may have been ignored</t>
-        </is>
-      </c>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -47521,7 +47513,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:23</t>
+          <t>gemessen: 2026-08-02 12:11</t>
         </is>
       </c>
     </row>
@@ -48680,9 +48672,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -48703,7 +48695,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>update: Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today. | filter: no sample value on the test instance — filter not probed</t>
+          <t>update: Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today.</t>
         </is>
       </c>
     </row>
@@ -50774,9 +50766,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -50795,11 +50787,7 @@
           <t>The ordered product.</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -52276,9 +52264,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -52299,7 +52287,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>create: The customer's own order / PO number (B2B standard field). Read-only upstream today; a clerk must be able to set and correct it. | filter: no sample value on the test instance — filter not probed | search: On the phone the customer quotes their PO number, not the ERP number — the full-text search must reach it.</t>
+          <t>create: The customer's own order / PO number (B2B standard field). Read-only upstream today; a clerk must be able to set and correct it. | search: On the phone the customer quotes their PO number, not the ERP number — the full-text search must reach it.</t>
         </is>
       </c>
     </row>
@@ -52334,9 +52322,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -52357,7 +52345,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>create: Technical shop / marketplace order id — today only the shop importer sets it; integrations need to set it too. | update: Technical shop / marketplace order id — today only the shop importer sets it; integrations need to set it too. | filter: no sample value on the test instance — filter not probed | search: Automated reconciliation matches by the external id.</t>
+          <t>create: Technical shop / marketplace order id — today only the shop importer sets it; integrations need to set it too. | update: Technical shop / marketplace order id — today only the shop importer sets it; integrations need to set it too. | search: Automated reconciliation matches by the external id.</t>
         </is>
       </c>
     </row>
@@ -52392,9 +52380,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -52415,7 +52403,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>create: Shop / marketplace order number — required to link an ERP order back to its source system. | update: Shop / marketplace order number — required to link an ERP order back to its source system. | filter: no sample value on the test instance — filter not probed | search: Support finds shop orders by the SHOP number the customer has.</t>
+          <t>create: Shop / marketplace order number — required to link an ERP order back to its source system. | update: Shop / marketplace order number — required to link an ERP order back to its source system. | search: Support finds shop orders by the SHOP number the customer has.</t>
         </is>
       </c>
     </row>
@@ -60942,7 +60930,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:24</t>
+          <t>gemessen: 2026-08-02 12:12</t>
         </is>
       </c>
     </row>
@@ -63631,9 +63619,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -63652,11 +63640,7 @@
           <t>The invoiced product.</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -70510,7 +70494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:25</t>
+          <t>gemessen: 2026-08-02 12:13</t>
         </is>
       </c>
     </row>
@@ -72329,9 +72313,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -72350,11 +72334,7 @@
           <t>The sales order this document came from. Filterable — the way to ask which documents an order produced.</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -72987,9 +72967,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -73008,11 +72988,7 @@
           <t>The delivered product.</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -74480,7 +74456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:26</t>
+          <t>gemessen: 2026-08-02 12:14</t>
         </is>
       </c>
     </row>
@@ -76161,9 +76137,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -76182,11 +76158,7 @@
           <t>The credited product.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -77247,9 +77219,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -77270,7 +77242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>create: The customer's PO number on the credit note (B2B) — read-only upstream today. | filter: no sample value on the test instance — filter not probed</t>
+          <t>create: The customer's PO number on the credit note (B2B) — read-only upstream today.</t>
         </is>
       </c>
     </row>
@@ -78599,7 +78571,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:27</t>
+          <t>gemessen: 2026-08-02 12:14</t>
         </is>
       </c>
     </row>
@@ -79696,9 +79668,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -79717,11 +79689,7 @@
           <t>The sales order this return refers to. Filterable — the way to ask which returns an order produced.</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -80242,9 +80210,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -80263,11 +80231,7 @@
           <t>The returned product.</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -80848,9 +80812,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -80871,7 +80835,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>create: The customer's PO number on the return — read-only upstream today. | update: The customer's PO number on the return — read-only upstream today. | filter: no sample value on the test instance — filter not probed</t>
+          <t>create: The customer's PO number on the return — read-only upstream today. | update: The customer's PO number on the return — read-only upstream today.</t>
         </is>
       </c>
     </row>
@@ -81781,7 +81745,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:27</t>
+          <t>gemessen: 2026-08-02 12:15</t>
         </is>
       </c>
     </row>
@@ -82550,9 +82514,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -82573,7 +82537,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>create: Requested delivery date at the supplier — not writable upstream today. | update: Requested delivery date at the supplier — not writable upstream today. | filter: no sample value on the test instance — filter not probed</t>
+          <t>create: Requested delivery date at the supplier — not writable upstream today. | update: Requested delivery date at the supplier — not writable upstream today.</t>
         </is>
       </c>
     </row>
@@ -83964,9 +83928,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -83985,11 +83949,7 @@
           <t>The ordered product.</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -85330,9 +85290,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -85353,7 +85313,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>create: The supplier's quote number we ordered against — read-only upstream today. | update: The supplier's quote number we ordered against — read-only upstream today. | filter: no sample value on the test instance — filter not probed</t>
+          <t>create: The supplier's quote number we ordered against — read-only upstream today. | update: The supplier's quote number we ordered against — read-only upstream today.</t>
         </is>
       </c>
     </row>

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lauf beendet: 2026-08-02 12:15</t>
+          <t>Lauf beendet: 2026-08-02 12:24</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-08-02 11:13</t>
+          <t>2026-08-02 12:24</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -17689,12 +17689,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Operations: list, read, create, update</t>
+          <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 11:13</t>
+          <t>gemessen: 2026-08-02 12:24</t>
         </is>
       </c>
     </row>
@@ -20446,11 +20446,7 @@
           <t>Product name shown on documents and in the shop.</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>create: created prd_61999 (labelled 'VT Verify') — no delete endpoint, left in place</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lauf beendet: 2026-08-02 12:24</t>
+          <t>Lauf beendet: 2026-08-02 14:51</t>
         </is>
       </c>
     </row>
@@ -1874,16 +1874,16 @@
         <v>56</v>
       </c>
       <c r="D31" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>263</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-08-02 10:59</t>
+          <t>2026-08-02 14:51</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:59</t>
+          <t>gemessen: 2026-08-02 14:51</t>
         </is>
       </c>
     </row>
@@ -4281,9 +4281,9 @@
           <t>Item id</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -4312,11 +4312,7 @@
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4334,9 +4330,9 @@
           <t>Object</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -4365,11 +4361,7 @@
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4387,9 +4379,9 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -4423,11 +4415,7 @@
           <t>The invoiced product.</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4445,9 +4433,9 @@
           <t>Quantity</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -4481,11 +4469,7 @@
           <t>Invoiced quantity with its unit.</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4503,9 +4487,9 @@
           <t>Unit</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -4539,11 +4523,7 @@
           <t>Unit of measure for the quantity.</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items.quantity', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4561,9 +4541,9 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -4597,11 +4577,7 @@
           <t>Invoiced amount (numeric quantity).</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items.quantity', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4619,9 +4595,9 @@
           <t>Unit price</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -4655,11 +4631,7 @@
           <t>Net price per unit on the invoice.</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4677,9 +4649,9 @@
           <t>Amount</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -4713,11 +4685,7 @@
           <t>Net price amount per unit.</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items.unitPrice', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4735,9 +4703,9 @@
           <t>Currency</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -4771,11 +4739,7 @@
           <t>Currency of the unit price.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items.unitPrice', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5853,9 +5817,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -5876,7 +5840,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>read: declared, but none of the 52 sampled records carries a value — nothing proven either way | filter: accepted, but returned nothing — the record the value came from is missing</t>
+          <t>read: declared, but none of the 52 sampled records carries a value — nothing proven either way | filter: no sample value on the test instance — filter not probed</t>
         </is>
       </c>
     </row>

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lauf beendet: 2026-08-02 14:51</t>
+          <t>Lauf beendet: 2026-08-02 15:02</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
         <v>56</v>
       </c>
       <c r="D31" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
         <v>5</v>
@@ -1883,10 +1883,10 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H31" t="n">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="I31" t="n">
         <v>12</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-08-02 14:51</t>
+          <t>2026-08-02 15:02</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3037,12 +3037,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Operations: list, read</t>
+          <t>Operations: list, read, update</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 14:51</t>
+          <t>gemessen: 2026-08-02 15:02</t>
         </is>
       </c>
     </row>
@@ -3411,14 +3411,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -3465,14 +3465,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -3739,14 +3739,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -3797,14 +3797,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -3851,14 +3851,14 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>read: declared, but none of the 52 sampled records carries a value — nothing proven either way</t>
+          <t>read: declared, but none of the 52 sampled records carries a value — nothing proven either way | update: no sample date value — not probed (a null date cannot be restored)</t>
         </is>
       </c>
     </row>
@@ -5587,14 +5587,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -5641,14 +5641,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lauf beendet: 2026-08-02 15:02</t>
+          <t>Lauf beendet: 2026-08-02 15:40</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
         <v>23</v>
       </c>
       <c r="D45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E45" t="n">
         <v>15</v>
@@ -2577,13 +2577,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-08-02 10:16</t>
+          <t>2026-08-02 15:40</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -2866,7 +2866,7 @@
         <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-08-02 10:16</t>
+          <t>2026-08-02 15:40</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -35750,12 +35750,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Operations: list, read</t>
+          <t>Operations: list, read, create, delete</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:16</t>
+          <t>gemessen: 2026-08-02 15:40</t>
         </is>
       </c>
     </row>
@@ -36804,9 +36804,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -36837,7 +36837,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>create: v1 CRUD exists upstream but is not orchestrated in this facade yet. | update: v1 CRUD exists upstream but is not orchestrated in this facade yet.</t>
+          <t>update: Renaming a storage location: the upstream PATCH exists (/api/v1/warehouses/{id}/storageLocations/{id}, answers 204) but the facade cannot address it — there is no detail read, so the location's warehouse has to be found by sweeping the list. Create is built and verified.</t>
         </is>
       </c>
     </row>
@@ -37086,9 +37086,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -37114,7 +37114,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>The warehouse this location belongs to. Filtering by it reads the warehouse-scoped upstream collection instead of paging the tenant.</t>
+          <t>The warehouse this location belongs to. Filtering by it reads the warehouse-scoped upstream collection instead of paging the tenant. REQUIRED on create: upstream has no standalone storage-location endpoint — a location is created underneath its warehouse.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -58414,12 +58414,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Operations: list</t>
+          <t>Operations: list, create, delete</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:16</t>
+          <t>gemessen: 2026-08-02 15:40</t>
         </is>
       </c>
     </row>
@@ -58560,9 +58560,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lauf beendet: 2026-08-02 15:40</t>
+          <t>Lauf beendet: 2026-08-02 15:58</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
         <v>23</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
         <v>15</v>
@@ -2583,7 +2583,7 @@
         <v>107</v>
       </c>
       <c r="I45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-08-02 15:40</t>
+          <t>2026-08-02 15:58</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -2866,7 +2866,7 @@
         <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-08-02 15:40</t>
+          <t>2026-08-02 15:58</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -35750,12 +35750,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Operations: list, read, create, delete</t>
+          <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 15:40</t>
+          <t>gemessen: 2026-08-02 15:58</t>
         </is>
       </c>
     </row>
@@ -36809,9 +36809,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -36835,11 +36835,7 @@
           <t>Location designation / bin label (e.g. 'A-01-03').</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>update: Renaming a storage location: the upstream PATCH exists (/api/v1/warehouses/{id}/storageLocations/{id}, answers 204) but the facade cannot address it — there is no detail read, so the location's warehouse has to be found by sweeping the list. Create is built and verified.</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -58414,12 +58410,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Operations: list, create, delete</t>
+          <t>Operations: list, create, update, delete</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 15:40</t>
+          <t>gemessen: 2026-08-02 15:58</t>
         </is>
       </c>
     </row>
@@ -58565,9 +58561,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -76,7 +76,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Shipment'!$A$4:$L$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Payment'!$A$4:$L$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'StockMovement'!$A$4:$L$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'StorageLocation'!$A$4:$L$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'StorageLocation'!$A$4:$L$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'StockLevel'!$A$4:$L$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'StockTake'!$A$4:$L$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'PickingRun'!$A$4:$L$37</definedName>
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lauf beendet: 2026-08-02 15:58</t>
+          <t>Lauf beendet: 2026-08-02 16:27</t>
         </is>
       </c>
     </row>
@@ -2565,25 +2565,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E45" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H45" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I45" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-08-02 15:58</t>
+          <t>2026-08-02 16:27</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -35723,7 +35723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -35755,7 +35755,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 15:58</t>
+          <t>gemessen: 2026-08-02 16:27</t>
         </is>
       </c>
     </row>
@@ -35824,32 +35824,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>capacity</t>
+          <t>abcCategory</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>select</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Capacity</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+          <t>ABC category</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>schwach</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -35868,26 +35868,31 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ABC classification driving picking priority — A = fastest movers, nearest the packing bench.</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>read: Capacity limits (max weight) for putaway decisions — not exposed via API today. | update: Capacity limits (max weight) for putaway decisions — not exposed via API today.</t>
+          <t>read: declared, but none of the 60 sampled records carries a value — nothing proven either way</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>capacity.maxWeight</t>
+          <t>contents</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Max weight</t>
+          <t>Contents</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -35921,6 +35926,11 @@
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>What lies on this location, composed from StockLevel. Filled on a SINGLE read only — on a list it would cost one extra call per row. Use StockLevel with filter[storageLocation] to query it directly. reserved stays empty: no per-location reservation exists upstream.</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>read: declared, but none of the 60 sampled records carries a value — nothing proven either way</t>
@@ -35930,17 +35940,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>capacity.maxWeight.unit</t>
+          <t>contents.batch</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -35976,29 +35986,29 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Unit of the maximum weight.</t>
+          <t>The batch / lot of that stored product, if batch-managed.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>read: no sampled record carries 'capacity.maxWeight', so the leaf could not be observed — nothing proven either way</t>
+          <t>read: no sampled record carries 'contents', so the leaf could not be observed — nothing proven either way</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>capacity.maxWeight.value</t>
+          <t>contents.product</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -36034,29 +36044,29 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Maximum load this location may hold.</t>
+          <t>A product currently stored in this location.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>read: no sampled record carries 'capacity.maxWeight', so the leaf could not be observed — nothing proven either way</t>
+          <t>read: no sampled record carries 'contents', so the leaf could not be observed — nothing proven either way</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>capacity.note</t>
+          <t>contents.quantity</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -36090,31 +36100,26 @@
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Free-text note on capacity or handling restrictions.</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>read: declared, but none of the 60 sampled records carries a value — nothing proven either way</t>
+          <t>read: no sampled record carries 'contents', so the leaf could not be observed — nothing proven either way</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>contents</t>
+          <t>contents.quantity.unit</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Contents</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -36150,29 +36155,29 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>What lies on this location, composed from StockLevel. Filled on a SINGLE read only — on a list it would cost one extra call per row. Use StockLevel with filter[storageLocation] to query it directly. reserved stays empty: no per-location reservation exists upstream.</t>
+          <t>Unit of the stored quantity.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>read: declared, but none of the 60 sampled records carries a value — nothing proven either way</t>
+          <t>read: no sampled record carries 'contents.quantity', so the leaf could not be observed — nothing proven either way</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>contents.batch</t>
+          <t>contents.quantity.value</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -36208,34 +36213,34 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>The batch / lot of that stored product, if batch-managed.</t>
+          <t>Physical quantity of that product/batch at this location.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>read: no sampled record carries 'contents', so the leaf could not be observed — nothing proven either way</t>
+          <t>read: no sampled record carries 'contents.quantity', so the leaf could not be observed — nothing proven either way</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>contents.product</t>
+          <t>contents.reserved</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -36264,31 +36269,26 @@
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>A product currently stored in this location.</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>read: no sampled record carries 'contents', so the leaf could not be observed — nothing proven either way</t>
+          <t>read: Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>contents.quantity</t>
+          <t>contents.reserved.unit</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -36322,26 +36322,31 @@
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Unit of the reserved quantity.</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>read: no sampled record carries 'contents', so the leaf could not be observed — nothing proven either way</t>
+          <t>read: no sampled record carries 'contents.reserved', so the leaf could not be observed — nothing proven either way</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>contents.quantity.unit</t>
+          <t>contents.reserved.value</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -36377,29 +36382,29 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Unit of the stored quantity.</t>
+          <t>Portion of that quantity already reserved for orders.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>read: no sampled record carries 'contents.quantity', so the leaf could not be observed — nothing proven either way</t>
+          <t>read: no sampled record carries 'contents.reserved', so the leaf could not be observed — nothing proven either way</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>contents.quantity.value</t>
+          <t>createdAt</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Created at</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -36435,44 +36440,44 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Physical quantity of that product/batch at this location.</t>
+          <t>Timestamp the record was created.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>read: no sampled record carries 'contents.quantity', so the leaf could not be observed — nothing proven either way</t>
+          <t>read: declared, but none of the 60 sampled records carries a value — nothing proven either way</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>contents.reserved</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>schwach</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -36493,29 +36498,29 @@
       <c r="J16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>read: Location contents are composed from the StockLevel projection now; the reserved portion per location stays unavailable — upstream reports reservations only as a product total.</t>
+          <t>read: declared, but none of the 60 sampled records carries a value — nothing proven either way | create: Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02. | update: Upstream returns the bin description but rejects it on create and update ("The attribute description is not allowed.") — the field is read-only for every API generation we have. Measured on mvp 2026-08-02.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>contents.reserved.unit</t>
+          <t>dimensions</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+          <t>Dimensions</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -36546,19 +36551,15 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Unit of the reserved quantity.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'contents.reserved', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+          <t>Physical size of the bin. Upstream carries length/width/height only — there is no weight limit, and the `capacity.maxWeight` this model used to declare did not exist anywhere.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>contents.reserved.value</t>
+          <t>dimensions.height</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -36568,22 +36569,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -36602,46 +36603,37 @@
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Portion of that quantity already reserved for orders.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'contents.reserved', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>createdAt</t>
+          <t>dimensions.length</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Created at</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -36660,31 +36652,22 @@
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Timestamp the record was created.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>read: declared, but none of the 60 sampled records carries a value — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>dimensions.width</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -36692,14 +36675,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -36718,42 +36701,37 @@
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>The record's stable, unique identifier — use it to read, link (references) and write this record. A typed 'speaking' id (e.g. cus_4711); assigned automatically when the record is created.</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kind</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -36774,14 +36752,10 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Purpose of the location: picking, bulk, inbound, returns, or quarantine.</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>read: Location kind (picking/bulk/inbound/returns/quarantine) and picking order drive WMS routing — the v1 list exposes only id/designation/warehouse. | create: Location kind (picking/bulk/inbound/returns/quarantine) and picking order drive WMS routing — the v1 list exposes only id/designation/warehouse. | update: Location kind (picking/bulk/inbound/returns/quarantine) and picking order drive WMS routing — the v1 list exposes only id/designation/warehouse.</t>
-        </is>
-      </c>
+          <t>The record's stable, unique identifier — use it to read, link (references) and write this record. A typed 'speaking' id (e.g. cus_4711); assigned automatically when the record is created.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -36907,19 +36881,19 @@
           <t>Picking order</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -36940,14 +36914,10 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Sort rank that defines the walking sequence when picking this warehouse.</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>read: declared, but none of the 60 sampled records carries a value — nothing proven either way</t>
-        </is>
-      </c>
+          <t>Sequence a picker walks the bins in (upstream `sort`).</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -37064,17 +37034,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>usage</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -37082,339 +37052,709 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>usage.blocked</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Blocked stock</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>The warehouse this location belongs to. Filtering by it reads the warehouse-scoped upstream collection instead of paging the tenant. REQUIRED on create: upstream has no standalone storage-location endpoint — a location is created underneath its warehouse.</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Sperrplatz: quarantine/quality hold — its stock is excluded from availability and auto-shipping. Same upstream flag the `status` field reports as blocked/active.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>Actions</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>usage.consumption</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Consumption location</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Verbrauchsplatz: stock booked out here is consumed, not shipped.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>destruktiv</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Beschreibung</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Notiz</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>usage.pointOfSale</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Point of sale</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Kassenplatz: stock sold over the counter.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>putaway</t>
+          <t>usage.production</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Put away</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Einlagern: book stock ONTO this location. Irreversible — a mistake is corrected by a counter-booking, not by an undo.</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>reachable — 422: storageLocation.putaway: invalid command</t>
-        </is>
-      </c>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Production access</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Fertigung darf von hier entnehmen.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>stockRemoval</t>
+          <t>usage.replenishment</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Stock removal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Auslagern: book stock OFF this location. Reduces stock and cannot be undone — only counter-booked.</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>reachable — 422: storageLocation.stockRemoval: invalid command</t>
-        </is>
-      </c>
+          <t>Replenishment location</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Nachschubplatz: stock is pulled from here to refill picking bins.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>warehouse</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>The warehouse this location belongs to. Filtering by it reads the warehouse-scoped upstream collection instead of paging the tenant. REQUIRED on create: upstream has no standalone storage-location endpoint — a location is created underneath its warehouse.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>destruktiv</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Beschreibung</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Notiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>putaway</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Put away</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Einlagern: book stock ONTO this location. Irreversible — a mistake is corrected by a counter-booking, not by an undo.</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>schwach</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>reachable — 422: storageLocation.putaway: invalid command</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>stockRemoval</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Stock removal</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Auslagern: book stock OFF this location. Reduces stock and cannot be undone — only counter-booked.</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>schwach</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>reachable — 422: storageLocation.stockRemoval: invalid command</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>stockTransfer</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Stock transfer</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Umlagern: move stock from THIS location to another one. Not atomic upstream — on a partial failure the removal is compensated and the outcome reported.</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>schwach</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>reachable — 422: storageLocation.stockTransfer: invalid command</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>inventoryCount</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Inventory count</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Inventur: record the COUNTED quantity of a product on this location; the difference to the book quantity is posted. The only repeatable stock write — counting the same result twice posts nothing the second time.</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>reachable — 422: storageLocation.inventoryCount: invalid command</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>stockAdjustment</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Stock adjustment</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Bestandskorrektur: post a known difference against this location. Requires a reason. Use inventoryCount when the counted quantity is known instead of the difference.</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>reachable — 422: storageLocation.stockAdjustment: invalid command</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>printLabel</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Print label</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Storage-location labels have no public endpoint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Process-Steps</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>destruktiv</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Beschreibung</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Notiz</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>inventoryCount</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Status › Block</t>
+          <t>Inventory count</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Inventur: record the COUNTED quantity of a product on this location; the difference to the book quantity is posted. The only repeatable stock write — counting the same result twice posts nothing the second time.</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>schwach</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>v1 storageLocations exposes no block/release state write.</t>
+          <t>reachable — 422: storageLocation.inventoryCount: invalid command</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>stockAdjustment</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Stock adjustment</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bestandskorrektur: post a known difference against this location. Requires a reason. Use inventoryCount when the counted quantity is known instead of the difference.</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>schwach</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>reachable — 422: storageLocation.stockAdjustment: invalid command</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>printLabel</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Print label</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Storage-location labels have no public endpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Process-Steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>destruktiv</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Beschreibung</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Notiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Status › Block</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>v1 storageLocations exposes no block/release state write.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>release</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Status › Release</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>v1 storageLocations exposes no block/release state write.</t>
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Wünsche ohne Feld (Lücke im Modell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Feld</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Facetten</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Begründung</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>locationType</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>v1 accepts a `locationType` on write with 204 but never returns it on any read, so a value written there cannot be verified or shown. Not modelled until upstream reads it back. Measured on mvp 2026-08-02.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L27"/>
+  <autoFilter ref="A4:L33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -66,7 +66,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Return'!$A$4:$L$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PurchaseOrder'!$A$4:$L$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'GoodsReceipt'!$A$4:$L$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'PurchaseInvoice'!$A$4:$L$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'PurchaseInvoice'!$A$4:$L$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Customer'!$A$4:$L$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Supplier'!$A$4:$L$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Channel'!$A$4:$L$18</definedName>
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lauf beendet: 2026-08-02 16:27</t>
+          <t>Lauf beendet: 2026-08-02 17:02</t>
         </is>
       </c>
     </row>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E31" t="n">
         <v>5</v>
@@ -1883,14 +1883,14 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
+        <v>20</v>
+      </c>
+      <c r="H31" t="n">
+        <v>243</v>
+      </c>
+      <c r="I31" t="n">
         <v>9</v>
       </c>
-      <c r="H31" t="n">
-        <v>249</v>
-      </c>
-      <c r="I31" t="n">
-        <v>12</v>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>4 (0/0)</t>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-08-02 15:02</t>
+          <t>2026-08-02 17:02</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3010,7 +3010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3037,12 +3037,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Operations: list, read, update</t>
+          <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 15:02</t>
+          <t>gemessen: 2026-08-02 17:02</t>
         </is>
       </c>
     </row>
@@ -3411,9 +3411,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -3465,9 +3465,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -3631,9 +3631,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -3739,9 +3739,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -3797,9 +3797,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -4223,19 +4223,19 @@
           <t>Items</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -4256,19 +4256,15 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Invoiced line items (products, quantities and prices).</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>read: BF lineItems exist on the record but are not mapped into the facade yet; write path pending the facade write-mapping. | create: BF lineItems exist on the record but are not mapped into the facade yet; write path pending the facade write-mapping. | update: BF lineItems exist on the record but are not mapped into the facade yet; write path pending the facade write-mapping.</t>
-        </is>
-      </c>
+          <t>Collection replace, the same contract the other documents use: an item WITH an id is updated, one WITHOUT an id is added, and an existing item OMITTED from the list is deleted.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>items.id</t>
+          <t>items.description</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4278,7 +4274,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Item id</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -4286,14 +4282,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -4312,12 +4308,16 @@
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>update: no sample value for description — not probed (a null line value cannot be restored net-zero)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>items.object</t>
+          <t>items.id</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Item id</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -4366,17 +4366,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>items.product</t>
+          <t>items.name</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -4384,14 +4384,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -4412,7 +4412,7 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>The invoiced product.</t>
+          <t>The text on the line. Ignored when `product` is set — upstream then fills it from the product record.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -4420,17 +4420,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>items.quantity</t>
+          <t>items.object</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -4464,27 +4464,22 @@
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Invoiced quantity with its unit.</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>items.quantity.unit</t>
+          <t>items.product</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4492,14 +4487,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -4520,25 +4515,29 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Unit of measure for the quantity.</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+          <t>Linking a product OVERRIDES the name: upstream fills productName from the product record.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>update: no sample value for product — not probed (a null line value cannot be restored net-zero)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>items.quantity.value</t>
+          <t>items.quantity</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4574,7 +4573,7 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Invoiced amount (numeric quantity).</t>
+          <t>Invoiced quantity with its unit.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4582,17 +4581,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>items.unitPrice</t>
+          <t>items.quantity.unit</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Unit price</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -4600,14 +4599,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -4628,7 +4627,7 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Net price per unit on the invoice.</t>
+          <t>Unit of measure for the quantity.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -4636,7 +4635,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>items.unitPrice.amount</t>
+          <t>items.quantity.value</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4646,7 +4645,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4654,14 +4653,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -4682,7 +4681,7 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Net price amount per unit.</t>
+          <t>Invoiced amount (numeric quantity).</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4690,17 +4689,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>items.unitPrice.currency</t>
+          <t>items.taxRate</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Tax rate</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -4708,14 +4707,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -4734,17 +4733,12 @@
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Currency of the unit price.</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>items.unitPrice</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4754,7 +4748,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Unit price</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -4790,7 +4784,7 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Read-only three-way match between order, goods receipt and invoice.</t>
+          <t>Net price per unit on the invoice.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4798,17 +4792,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>match.goodsCheck</t>
+          <t>items.unitPrice.amount</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Goods check</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -4816,14 +4810,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -4844,7 +4838,7 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Goods-receipt check result of the match.</t>
+          <t>Net price amount per unit.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4852,7 +4846,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>match.invoiceCheck</t>
+          <t>items.unitPrice.currency</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4862,7 +4856,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Invoice check</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -4870,14 +4864,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -4898,7 +4892,7 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Invoice check result of the match.</t>
+          <t>Currency of the unit price.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -4906,17 +4900,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>match.purchaseOrder</t>
+          <t>match</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Purchase order</t>
+          <t>Match</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -4952,7 +4946,7 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>The purchase order the invoice is matched against.</t>
+          <t>Read-only three-way match between order, goods receipt and invoice.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -4960,17 +4954,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>match.status</t>
+          <t>match.goodsCheck</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Goods check</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -4983,9 +4977,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -5006,19 +5000,15 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Overall match result: pending, matched, or mismatch.</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>update: Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
-        </is>
-      </c>
+          <t>Goods-receipt check result of the match.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>match.invoiceCheck</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5028,7 +5018,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Invoice check</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -5036,19 +5026,19 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -5062,26 +5052,27 @@
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>create: REVISED (docs/05 #6): the BF entity supplierInvoice HAS full CRUD incl. goods/invoice check — the remaining work is OUR facade write-mapping + live write verification, not a new Xentral API. | update: REVISED (docs/05 #6): the BF entity supplierInvoice HAS full CRUD incl. goods/invoice check — the remaining work is OUR facade write-mapping + live write verification, not a new Xentral API.</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Invoice check result of the match.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>match.purchaseOrder</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Purchase order</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -5117,7 +5108,7 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Type discriminator of the record (its entity name).</t>
+          <t>The purchase order the invoice is matched against.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -5125,17 +5116,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>payment</t>
+          <t>match.status</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>select</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -5148,9 +5139,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -5171,25 +5162,29 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Payment method, terms and status for the invoice.</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
+          <t>Overall match result: pending, matched, or mismatch.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>update: Re-running/overriding the match verdict via API (rematch) — the check statuses are readable now; a command to re-evaluate is still missing upstream.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>payment.discountUntil</t>
+          <t>number</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Discount until</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -5197,19 +5192,19 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -5223,27 +5218,26 @@
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Last date the cash-discount (Skonto) can be taken.</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>create: The document number is system-assigned: sending `documentNumber` on create answers 201 and the record comes back with an empty number (measured on mvp 2026-08-02). Same behaviour as the other documents. | update: The document number is system-assigned: sending `documentNumber` on create answers 201 and the record comes back with an empty number (measured on mvp 2026-08-02). Same behaviour as the other documents.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>payment.dueDate</t>
+          <t>object</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Due date</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -5279,7 +5273,7 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Date the invoice is payable by.</t>
+          <t>Type discriminator of the record (its entity name).</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -5287,22 +5281,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>payment.method</t>
+          <t>payment</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -5333,19 +5327,15 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Payment method used to settle the invoice.</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>read: declared, but none of the 52 sampled records carries a value — nothing proven either way</t>
-        </is>
-      </c>
+          <t>Payment method, terms and status for the invoice.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>payment.paidOn</t>
+          <t>payment.discountUntil</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5355,7 +5345,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Paid on</t>
+          <t>Discount until</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -5363,9 +5353,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -5391,7 +5381,7 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Date the invoice was paid.</t>
+          <t>Last date the cash-discount (Skonto) can be taken.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -5399,17 +5389,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>payment.status</t>
+          <t>payment.dueDate</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Payment status</t>
+          <t>Due date</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -5417,9 +5407,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -5427,9 +5417,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -5445,34 +5435,30 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Payment state of the invoice (e.g. open, paid).</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>filter: Open-liabilities view needs filtering by payment status — not allowed on the BF supplierInvoice API today.</t>
-        </is>
-      </c>
+          <t>Date the invoice is payable by.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>references</t>
+          <t>payment.method</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>References</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>schwach</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -5503,30 +5489,34 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>External references on the supplier invoice.</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
+          <t>Payment method used to settle the invoice.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>read: declared, but none of the 52 sampled records carries a value — nothing proven either way</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>references.creditorAccountNumber</t>
+          <t>payment.paidOn</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Creditor account</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+          <t>Paid on</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -5557,29 +5547,25 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Creditor (A/P) account the invoice is booked to.</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>read: declared, but none of the 52 sampled records carries a value — nothing proven either way</t>
-        </is>
-      </c>
+          <t>Date the invoice was paid.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>references.externalReference</t>
+          <t>payment.status</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>select</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>External reference</t>
+          <t>Payment status</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -5587,19 +5573,19 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -5615,25 +5601,29 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Additional external reference for the invoice.</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
+          <t>Payment state of the invoice (e.g. open, paid).</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>filter: Open-liabilities view needs filtering by payment status — not allowed on the BF supplierInvoice API today.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>references.supplierInvoiceNumber</t>
+          <t>references</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Supplier invoice number</t>
+          <t>References</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -5641,19 +5631,19 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -5661,15 +5651,15 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>The invoice number printed on the supplier's document.</t>
+          <t>External references on the supplier invoice.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -5677,22 +5667,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>references.creditorAccountNumber</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>Creditor account</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>schwach</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -5705,9 +5695,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -5723,29 +5713,29 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Workflow state of the supplier invoice: received, matched, approved, paid, or rejected.</t>
+          <t>Creditor (A/P) account the invoice is booked to.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>filter: Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
+          <t>read: declared, but none of the 52 sampled records carries a value — nothing proven either way</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>supplier</t>
+          <t>references.externalReference</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>External reference</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -5753,14 +5743,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -5781,7 +5771,7 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>The supplier who issued the invoice.</t>
+          <t>Additional external reference for the invoice.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -5789,37 +5779,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>references.supplierInvoiceNumber</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>tag</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tags</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>Supplier invoice number</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -5827,37 +5817,33 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Free-text labels for grouping/segmenting the record.</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>read: declared, but none of the 52 sampled records carries a value — nothing proven either way | filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+          <t>The invoice number printed on the supplier's document.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>totals</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>embedded</t>
+          <t>select</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -5875,9 +5861,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -5893,25 +5879,29 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Read-only invoice totals.</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
+          <t>Workflow state of the supplier invoice: received, matched, approved, paid, or rejected.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>filter: Filtering incoming invoices by workflow status is the AP daily view — the BF supplierInvoice API does not allow filtering documentStatus today.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>totals.currency</t>
+          <t>supplier</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -5919,14 +5909,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -5947,7 +5937,7 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Currency of the totals.</t>
+          <t>The creditor. REQUIRED on create by this core, not by upstream: an empty POST is accepted and produces an invoice with no creditor, no dates and no positions.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -5955,22 +5945,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>totals.gross</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gross</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>schwach</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -5983,9 +5973,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -6001,25 +5991,29 @@
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Gross invoice total (incl. tax).</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
+          <t>Free-text labels for grouping/segmenting the record.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>read: declared, but none of the 52 sampled records carries a value — nothing proven either way | filter: no sample value on the test instance — filter not probed</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>totals.outstanding</t>
+          <t>totals</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>embedded</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Outstanding</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -6055,7 +6049,7 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Amount still outstanding (gross minus paid).</t>
+          <t>Read-only invoice totals.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -6063,7 +6057,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>totals.paid</t>
+          <t>totals.currency</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6073,7 +6067,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Paid</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -6109,7 +6103,7 @@
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Amount already paid on the invoice.</t>
+          <t>Currency of the totals.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -6117,17 +6111,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>updatedAt</t>
+          <t>totals.gross</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Updated at</t>
+          <t>Gross</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -6150,9 +6144,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -6163,131 +6157,221 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
+          <t>Gross invoice total (incl. tax).</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>totals.outstanding</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Outstanding</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Amount still outstanding (gross minus paid).</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>totals.paid</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Amount already paid on the invoice.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>updatedAt</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Updated at</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>Timestamp the record was last changed.</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
+      <c r="L63" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
         <is>
           <t>Actions</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>destruktiv</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Beschreibung</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Notiz</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>rematch</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Re-run 3-way match</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Matching runs upstream automatically; no re-trigger endpoint is exposed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>registerPayment</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Register payment</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>The payments API is not public — no endpoint to register an outgoing payment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>schedulePayment</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Schedule payment</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Payment runs have no public API.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>attachFile</t>
+          <t>rematch</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Attach file</t>
+          <t>Re-run 3-way match</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -6299,99 +6383,171 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
+          <t>Matching runs upstream automatically; no re-trigger endpoint is exposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>registerPayment</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Register payment</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>The payments API is not public — no endpoint to register an outgoing payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>schedulePayment</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Schedule payment</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Payment runs have no public API.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>attachFile</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Attach file</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>Wunsch</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>Candidate: v1 liabilities/{id}/documents (upload) — needs the numeric id, which the BF rows do not carry.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
         <is>
           <t>Process-Steps</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>destruktiv</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Beschreibung</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Notiz</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>approve</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>Document status › Approve</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>The BF InvoiceCheck/DocumentStatus process steps are readable, but the write transition is not exposed. Candidate: v1 liabilities/{id}/actions/release — needs the numeric id, which the BF rows do not carry.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>reject</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Document status › Reject</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Rejecting has no exposed write transition.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L60"/>
+  <autoFilter ref="A4:L63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/cores/agentos_neo_xentral/verified.xlsx
+++ b/cores/agentos_neo_xentral/verified.xlsx
@@ -130,7 +130,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -167,11 +167,6 @@
         <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4B183"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -185,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -204,9 +199,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -609,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lauf beendet: 2026-08-02 10:27</t>
+          <t>Lauf beendet: 2026-08-02 15:58</t>
         </is>
       </c>
     </row>
@@ -894,7 +886,7 @@
         <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -903,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>264</v>
@@ -923,7 +915,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-08-02 10:26</t>
+          <t>2026-08-02 12:14</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -947,19 +939,19 @@
         <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E12" t="n">
         <v>25</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H12" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I12" t="n">
         <v>36</v>
@@ -976,7 +968,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-08-02 10:13</t>
+          <t>2026-08-02 11:35</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1000,7 +992,7 @@
         <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E13" t="n">
         <v>25</v>
@@ -1009,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>253</v>
@@ -1029,7 +1021,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-08-02 10:25</t>
+          <t>2026-08-02 12:13</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1588,13 +1580,13 @@
         <v>98</v>
       </c>
       <c r="D25" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E25" t="n">
         <v>34</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>45</v>
@@ -1617,7 +1609,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-08-02 10:15</t>
+          <t>2026-08-02 12:24</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -1882,19 +1874,19 @@
         <v>56</v>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H31" t="n">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="I31" t="n">
         <v>12</v>
@@ -1911,7 +1903,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-08-02 10:12</t>
+          <t>2026-08-02 15:02</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -1931,7 +1923,7 @@
         <v>73</v>
       </c>
       <c r="D32" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E32" t="n">
         <v>14</v>
@@ -1940,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>297</v>
@@ -1960,7 +1952,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-08-02 10:27</t>
+          <t>2026-08-02 12:15</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2033,16 +2025,16 @@
         <v>81</v>
       </c>
       <c r="D34" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
         <v>308</v>
@@ -2062,7 +2054,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-08-02 10:21</t>
+          <t>2026-08-02 12:09</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2086,7 +2078,7 @@
         <v>48</v>
       </c>
       <c r="D35" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E35" t="n">
         <v>11</v>
@@ -2095,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
         <v>178</v>
@@ -2115,7 +2107,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-08-02 10:27</t>
+          <t>2026-08-02 12:14</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2188,7 +2180,7 @@
         <v>90</v>
       </c>
       <c r="D37" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E37" t="n">
         <v>26</v>
@@ -2197,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
         <v>367</v>
@@ -2217,7 +2209,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-08-02 10:24</t>
+          <t>2026-08-02 12:12</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2241,7 +2233,7 @@
         <v>121</v>
       </c>
       <c r="D38" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E38" t="n">
         <v>40</v>
@@ -2250,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H38" t="n">
         <v>487</v>
@@ -2270,7 +2262,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-08-02 10:23</t>
+          <t>2026-08-02 12:11</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2576,7 +2568,7 @@
         <v>23</v>
       </c>
       <c r="D45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
         <v>15</v>
@@ -2585,13 +2577,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2605,7 +2597,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-08-02 10:16</t>
+          <t>2026-08-02 15:58</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -2625,19 +2617,19 @@
         <v>84</v>
       </c>
       <c r="D46" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E46" t="n">
         <v>29</v>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H46" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I46" t="n">
         <v>33</v>
@@ -2654,7 +2646,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-08-02 10:14</t>
+          <t>2026-08-02 11:36</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -2874,7 +2866,7 @@
         <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2886,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2903,7 +2895,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-08-02 10:16</t>
+          <t>2026-08-02 15:58</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -3045,12 +3037,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Operations: list, read</t>
+          <t>Operations: list, read, update</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:12</t>
+          <t>gemessen: 2026-08-02 15:02</t>
         </is>
       </c>
     </row>
@@ -3419,14 +3411,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -3473,14 +3465,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -3747,14 +3739,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -3805,14 +3797,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -3859,14 +3851,14 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -3892,7 +3884,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>read: declared, but none of the 52 sampled records carries a value — nothing proven either way</t>
+          <t>read: declared, but none of the 52 sampled records carries a value — nothing proven either way | update: no sample date value — not probed (a null date cannot be restored)</t>
         </is>
       </c>
     </row>
@@ -4289,9 +4281,9 @@
           <t>Item id</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -4320,11 +4312,7 @@
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4342,9 +4330,9 @@
           <t>Object</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -4373,11 +4361,7 @@
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4395,9 +4379,9 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -4431,11 +4415,7 @@
           <t>The invoiced product.</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4453,9 +4433,9 @@
           <t>Quantity</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -4489,11 +4469,7 @@
           <t>Invoiced quantity with its unit.</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4511,9 +4487,9 @@
           <t>Unit</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -4547,11 +4523,7 @@
           <t>Unit of measure for the quantity.</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items.quantity', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4569,9 +4541,9 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -4605,11 +4577,7 @@
           <t>Invoiced amount (numeric quantity).</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items.quantity', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4627,9 +4595,9 @@
           <t>Unit price</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -4663,11 +4631,7 @@
           <t>Net price per unit on the invoice.</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4685,9 +4649,9 @@
           <t>Amount</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -4721,11 +4685,7 @@
           <t>Net price amount per unit.</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items.unitPrice', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4743,9 +4703,9 @@
           <t>Currency</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -4779,11 +4739,7 @@
           <t>Currency of the unit price.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>read: no sampled record carries 'items.unitPrice', so the leaf could not be observed — nothing proven either way</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5631,14 +5587,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -5685,14 +5641,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -5705,9 +5661,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -5716,11 +5672,7 @@
           <t>The invoice number printed on the supplier's document.</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>search: declared searchable, but not part of this entity's search fan-out — searchFields is empty, so a consolidated search never looks at this field</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5865,9 +5817,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -5888,7 +5840,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>read: declared, but none of the 52 sampled records carries a value — nothing proven either way | filter: accepted, but returned nothing — the record the value came from is missing</t>
+          <t>read: declared, but none of the 52 sampled records carries a value — nothing proven either way | filter: no sample value on the test instance — filter not probed</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6434,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:13</t>
+          <t>gemessen: 2026-08-02 11:35</t>
         </is>
       </c>
     </row>
@@ -6633,9 +6585,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -6643,20 +6595,20 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>City / town.</t>
+          <t>City / town. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -6745,9 +6697,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -6755,20 +6707,20 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ISO country code (e.g. DE).</t>
+          <t>ISO country code (e.g. DE). Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -7189,9 +7141,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -7199,20 +7151,20 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>State / region / province.</t>
+          <t>State / region / province. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -7247,9 +7199,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -7257,20 +7209,20 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Street and house number.</t>
+          <t>Street and house number. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -7363,9 +7315,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -7373,20 +7325,20 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Postal code.</t>
+          <t>Postal code. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11446,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:14</t>
+          <t>gemessen: 2026-08-02 11:36</t>
         </is>
       </c>
     </row>
@@ -11645,9 +11597,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -11655,20 +11607,20 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>City / town.</t>
+          <t>City / town. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -11757,9 +11709,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -11767,20 +11719,20 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ISO country code (e.g. DE).</t>
+          <t>ISO country code (e.g. DE). Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -12205,9 +12157,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -12215,20 +12167,20 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>State / region / province.</t>
+          <t>State / region / province. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -12263,9 +12215,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -12273,20 +12225,20 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Street and house number.</t>
+          <t>Street and house number. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -12379,9 +12331,9 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -12389,20 +12341,20 @@
           <t>schwach</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Postal code.</t>
+          <t>Postal code. Filtering, sorting and search on this leaf reach the MAIN address only — upstream maps it to a column on the partner record, so a delivery or deviating-billing row carrying the value is not matched (measured on mvp: a customer whose shipping city is 'Musterort' is not returned by addresses.city=Musterort). Query the deliveryAddresses sub-resource for those.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>filter: no sample value on the test instance — filter not probed | sort: fewer than two distinct values on the page — order not assertable | search: declared searchable, but not part of this entity's search fan-out — searchFields is ['email', 'name', 'number'], so a consolidated search never looks at this field</t>
+          <t>sort: fewer than two distinct values on the page — order not assertable</t>
         </is>
       </c>
     </row>
@@ -17701,12 +17653,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Operations: list, read, create, update</t>
+          <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:15</t>
+          <t>gemessen: 2026-08-02 12:24</t>
         </is>
       </c>
     </row>
@@ -18945,9 +18897,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>FEHLER</t>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -18956,11 +18908,7 @@
           <t>EAN / GTIN barcode of the product.</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>search: declared searchable, but not part of this entity's search fan-out — searchFields is ['name', 'number'], so a consolidated search never looks at this field</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -20462,11 +20410,7 @@
           <t>Product name shown on documents and in the shop.</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>create: created prd_61998 (labelled 'VT Verify') — no delete endpoint, left in place</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -30876,7 +30820,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:21</t>
+          <t>gemessen: 2026-08-02 12:09</t>
         </is>
       </c>
     </row>
@@ -32841,9 +32785,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -32862,11 +32806,7 @@
           <t>The quoted product.</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -34923,9 +34863,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>schwach</t>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -34944,11 +34884,7 @@
           <t>Free-text labels for grouping/segmenting the record.</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>filter: accepted, but the page does not contain the record the value came from — the filter may have been ignored</t>
-        </is>
-      </c>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -35814,12 +35750,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Operations: list, read</t>
+          <t>Operations: list, read, create, update, delete</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:16</t>
+          <t>gemessen: 2026-08-02 15:58</t>
         </is>
       </c>
     </row>
@@ -36868,14 +36804,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Wunsch</t>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -36899,11 +36835,7 @@
           <t>Location designation / bin label (e.g. 'A-01-03').</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>create: v1 CRUD exists upstream but is not orchestrated in this facade yet. | update: v1 CRUD exists upstream but is not orchestrated in this facade yet.</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -37150,9 +37082,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>offen</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -37178,7 +37110,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>The warehouse this location belongs to. Filtering by it reads the warehouse-scoped upstream collection instead of paging the tenant.</t>
+          <t>The warehouse this location belongs to. Filtering by it reads the warehouse-scoped upstream collection instead of paging the tenant. REQUIRED on create: upstream has no standalone storage-location endpoint — a location is created underneath its warehouse.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -47537,7 +47469,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:23</t>
+          <t>gemessen: 2026-08-02 12:11</t>
         </is>
       </c>
     </row>
@@ -48696,9 +48628,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -48719,7 +48651,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>update: Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today. | filter: no sample value on the test instance — filter not probed</t>
+          <t>update: Desired delivery date — core fulfilment field; one of the first things entered on an order. Not writable upstream today.</t>
         </is>
       </c>
     </row>
@@ -50790,9 +50722,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -50811,11 +50743,7 @@
           <t>The ordered product.</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -52292,9 +52220,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -52315,7 +52243,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>create: The customer's own order / PO number (B2B standard field). Read-only upstream today; a clerk must be able to set and correct it. | filter: no sample value on the test instance — filter not probed | search: On the phone the customer quotes their PO number, not the ERP number — the full-text search must reach it.</t>
+          <t>create: The customer's own order / PO number (B2B standard field). Read-only upstream today; a clerk must be able to set and correct it. | search: On the phone the customer quotes their PO number, not the ERP number — the full-text search must reach it.</t>
         </is>
       </c>
     </row>
@@ -52350,9 +52278,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -52373,7 +52301,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>create: Technical shop / marketplace order id — today only the shop importer sets it; integrations need to set it too. | update: Technical shop / marketplace order id — today only the shop importer sets it; integrations need to set it too. | filter: no sample value on the test instance — filter not probed | search: Automated reconciliation matches by the external id.</t>
+          <t>create: Technical shop / marketplace order id — today only the shop importer sets it; integrations need to set it too. | update: Technical shop / marketplace order id — today only the shop importer sets it; integrations need to set it too. | search: Automated reconciliation matches by the external id.</t>
         </is>
       </c>
     </row>
@@ -52408,9 +52336,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -52431,7 +52359,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>create: Shop / marketplace order number — required to link an ERP order back to its source system. | update: Shop / marketplace order number — required to link an ERP order back to its source system. | filter: no sample value on the test instance — filter not probed | search: Support finds shop orders by the SHOP number the customer has.</t>
+          <t>create: Shop / marketplace order number — required to link an ERP order back to its source system. | update: Shop / marketplace order number — required to link an ERP order back to its source system. | search: Support finds shop orders by the SHOP number the customer has.</t>
         </is>
       </c>
     </row>
@@ -58482,12 +58410,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Operations: list</t>
+          <t>Operations: list, create, update, delete</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:16</t>
+          <t>gemessen: 2026-08-02 15:58</t>
         </is>
       </c>
     </row>
@@ -58628,14 +58556,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -60958,7 +60886,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:24</t>
+          <t>gemessen: 2026-08-02 12:12</t>
         </is>
       </c>
     </row>
@@ -63647,9 +63575,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -63668,11 +63596,7 @@
           <t>The invoiced product.</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -70526,7 +70450,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:25</t>
+          <t>gemessen: 2026-08-02 12:13</t>
         </is>
       </c>
     </row>
@@ -72345,9 +72269,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -72366,11 +72290,7 @@
           <t>The sales order this document came from. Filterable — the way to ask which documents an order produced.</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -73003,9 +72923,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -73024,11 +72944,7 @@
           <t>The delivered product.</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -74496,7 +74412,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:26</t>
+          <t>gemessen: 2026-08-02 12:14</t>
         </is>
       </c>
     </row>
@@ -76177,9 +76093,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -76198,11 +76114,7 @@
           <t>The credited product.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -77263,9 +77175,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -77286,7 +77198,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>create: The customer's PO number on the credit note (B2B) — read-only upstream today. | filter: no sample value on the test instance — filter not probed</t>
+          <t>create: The customer's PO number on the credit note (B2B) — read-only upstream today.</t>
         </is>
       </c>
     </row>
@@ -78615,7 +78527,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:27</t>
+          <t>gemessen: 2026-08-02 12:14</t>
         </is>
       </c>
     </row>
@@ -79712,9 +79624,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -79733,11 +79645,7 @@
           <t>The sales order this return refers to. Filterable — the way to ask which returns an order produced.</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -80258,9 +80166,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -80279,11 +80187,7 @@
           <t>The returned product.</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -80864,9 +80768,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -80887,7 +80791,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>create: The customer's PO number on the return — read-only upstream today. | update: The customer's PO number on the return — read-only upstream today. | filter: no sample value on the test instance — filter not probed</t>
+          <t>create: The customer's PO number on the return — read-only upstream today. | update: The customer's PO number on the return — read-only upstream today.</t>
         </is>
       </c>
     </row>
@@ -81797,7 +81701,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemessen: 2026-08-02 10:27</t>
+          <t>gemessen: 2026-08-02 12:15</t>
         </is>
       </c>
     </row>
@@ -82566,9 +82470,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -82589,7 +82493,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>create: Requested delivery date at the supplier — not writable upstream today. | update: Requested delivery date at the supplier — not writable upstream today. | filter: no sample value on the test instance — filter not probed</t>
+          <t>create: Requested delivery date at the supplier — not writable upstream today. | update: Requested delivery date at the supplier — not writable upstream today.</t>
         </is>
       </c>
     </row>
@@ -83980,9 +83884,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -84001,11 +83905,7 @@
           <t>The ordered product.</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>filter: no sample value on the test instance — filter not probed</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -85346,9 +85246,9 @@
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -85369,7 +85269,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>create: The supplier's quote number we ordered against — read-only upstream today. | update: The supplier's quote number we ordered against — read-only upstream today. | filter: no sample value on the test instance — filter not probed</t>
+          <t>create: The supplier's quote number we ordered against — read-only upstream today. | update: The supplier's quote number we ordered against — read-only upstream today.</t>
         </is>
       </c>
     </row>
